--- a/SC reuslts/some results NSGAII.xlsx
+++ b/SC reuslts/some results NSGAII.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahbub\Documents\GitHub\EnergyPLANDomainKnowledgeEAStep1\SC reuslts\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11385"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11385" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="ZDT1" sheetId="1" r:id="rId1"/>
@@ -18,11 +13,14 @@
     <sheet name="ZDT4" sheetId="4" r:id="rId4"/>
     <sheet name="ZDT6" sheetId="5" r:id="rId5"/>
     <sheet name="DTLZ2" sheetId="6" r:id="rId6"/>
+    <sheet name="DTLZ5" sheetId="8" r:id="rId7"/>
+    <sheet name="summary" sheetId="7" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="25">
   <si>
     <t>terminate generation</t>
   </si>
@@ -63,12 +61,57 @@
   <si>
     <t>average HV percentage</t>
   </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>ZDT1</t>
+  </si>
+  <si>
+    <t>NoSFE</t>
+  </si>
+  <si>
+    <t>HVd</t>
+  </si>
+  <si>
+    <t>epsd</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>HVper</t>
+  </si>
+  <si>
+    <t>NSGAII</t>
+  </si>
+  <si>
+    <t>ZDT2</t>
+  </si>
+  <si>
+    <t>ZDT4</t>
+  </si>
+  <si>
+    <t>ZDT3</t>
+  </si>
+  <si>
+    <t>DTLZ2</t>
+  </si>
+  <si>
+    <t>SPEA2</t>
+  </si>
+  <si>
+    <t>DTLZ5</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -105,17 +148,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -146,17 +237,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -189,8 +270,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -198,33 +277,11 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
-        </a:p>
-      </c:txPr>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1748,23 +1805,14 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="590640568"/>
-        <c:axId val="590639392"/>
+        <c:axId val="67547136"/>
+        <c:axId val="67549056"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="590640568"/>
+        <c:axId val="67547136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
@@ -1806,8 +1854,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1815,29 +1861,8 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="it-IT"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1869,19 +1894,18 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="590639392"/>
+        <c:crossAx val="67549056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="590639392"/>
+        <c:axId val="67549056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -1923,8 +1947,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1932,30 +1954,9 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="it-IT"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1987,10 +1988,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="590640568"/>
+        <c:crossAx val="67547136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2004,7 +2005,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2028,571 +2028,15 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3287,7 +2731,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -5792,6 +5236,2557 @@
         </row>
       </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="ZDT1"/>
+      <sheetName val="ZDT2"/>
+      <sheetName val="ZDT3"/>
+      <sheetName val="ZDT4"/>
+      <sheetName val="ZDT6"/>
+      <sheetName val="DTLZ2"/>
+      <sheetName val="DTLZ5"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="C4">
+            <v>1300</v>
+          </cell>
+          <cell r="D4">
+            <v>1.60814068969328E-3</v>
+          </cell>
+          <cell r="E4">
+            <v>0.98366836607609498</v>
+          </cell>
+          <cell r="F4">
+            <v>-4.02775403213009E-3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>-9900</v>
+          </cell>
+          <cell r="D5">
+            <v>-3.16655889626482E-3</v>
+          </cell>
+          <cell r="E5">
+            <v>0.99206811629410796</v>
+          </cell>
+          <cell r="F5">
+            <v>3.1351622381991999E-3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>200</v>
+          </cell>
+          <cell r="D6">
+            <v>4.6621486955444803E-6</v>
+          </cell>
+          <cell r="E6">
+            <v>0.98802086335336203</v>
+          </cell>
+          <cell r="F6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>-7200</v>
+          </cell>
+          <cell r="D7">
+            <v>-4.0099491828714503E-3</v>
+          </cell>
+          <cell r="E7">
+            <v>0.99098020893454297</v>
+          </cell>
+          <cell r="F7">
+            <v>3.5947162432393501E-3</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>-6200</v>
+          </cell>
+          <cell r="D8">
+            <v>-3.3441061808248099E-3</v>
+          </cell>
+          <cell r="E8">
+            <v>0.99130369855643297</v>
+          </cell>
+          <cell r="F8">
+            <v>2.8522046475236702E-3</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>-15100</v>
+          </cell>
+          <cell r="D9">
+            <v>-3.82786054555905E-3</v>
+          </cell>
+          <cell r="E9">
+            <v>0.99297231938666697</v>
+          </cell>
+          <cell r="F9">
+            <v>3.6982122083177799E-3</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>3900</v>
+          </cell>
+          <cell r="D10">
+            <v>4.5017302078086399E-3</v>
+          </cell>
+          <cell r="E10">
+            <v>0.981232831281032</v>
+          </cell>
+          <cell r="F10">
+            <v>-2.7118335422688599E-3</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>2400</v>
+          </cell>
+          <cell r="D11">
+            <v>2.5505636518632301E-3</v>
+          </cell>
+          <cell r="E11">
+            <v>0.983337390069569</v>
+          </cell>
+          <cell r="F11">
+            <v>-1.2344848441289101E-3</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>600</v>
+          </cell>
+          <cell r="D12">
+            <v>3.7394611542596002E-4</v>
+          </cell>
+          <cell r="E12">
+            <v>0.987996746859789</v>
+          </cell>
+          <cell r="F12">
+            <v>-6.4374001771883005E-4</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>-11000</v>
+          </cell>
+          <cell r="D13">
+            <v>-3.16715950000234E-3</v>
+          </cell>
+          <cell r="E13">
+            <v>0.99238881467912599</v>
+          </cell>
+          <cell r="F13">
+            <v>6.2472665566742902E-4</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>-10900</v>
+          </cell>
+          <cell r="D14">
+            <v>-3.5445891426811801E-3</v>
+          </cell>
+          <cell r="E14">
+            <v>0.992490469791112</v>
+          </cell>
+          <cell r="F14">
+            <v>1.2462163371180701E-3</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>-9700</v>
+          </cell>
+          <cell r="D15">
+            <v>-3.31050688242662E-3</v>
+          </cell>
+          <cell r="E15">
+            <v>0.99176246229203902</v>
+          </cell>
+          <cell r="F15">
+            <v>3.2980982086585598E-3</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>-3700</v>
+          </cell>
+          <cell r="D16">
+            <v>-1.77546741219625E-3</v>
+          </cell>
+          <cell r="E16">
+            <v>0.98890438295470895</v>
+          </cell>
+          <cell r="F16">
+            <v>1.5353722018479701E-3</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>1500</v>
+          </cell>
+          <cell r="D17">
+            <v>9.4272468865297301E-4</v>
+          </cell>
+          <cell r="E17">
+            <v>0.98645413286175898</v>
+          </cell>
+          <cell r="F17">
+            <v>-1.52577647807916E-3</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>1200</v>
+          </cell>
+          <cell r="D18">
+            <v>1.3039394726654899E-3</v>
+          </cell>
+          <cell r="E18">
+            <v>0.98406834188999204</v>
+          </cell>
+          <cell r="F18">
+            <v>-6.3733362332385403E-4</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>-4000</v>
+          </cell>
+          <cell r="D19">
+            <v>-2.0285364710366199E-3</v>
+          </cell>
+          <cell r="E19">
+            <v>0.98985493947810699</v>
+          </cell>
+          <cell r="F19">
+            <v>2.8183815968217899E-3</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>-6400</v>
+          </cell>
+          <cell r="D20">
+            <v>-2.29381873342959E-3</v>
+          </cell>
+          <cell r="E20">
+            <v>0.99147126606074298</v>
+          </cell>
+          <cell r="F20">
+            <v>1.6771180654425999E-3</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>-2600</v>
+          </cell>
+          <cell r="D21">
+            <v>-1.20860640175202E-3</v>
+          </cell>
+          <cell r="E21">
+            <v>0.989810317096536</v>
+          </cell>
+          <cell r="F21">
+            <v>2.1832283042739699E-3</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>-9200</v>
+          </cell>
+          <cell r="D22">
+            <v>-3.5371720568281302E-3</v>
+          </cell>
+          <cell r="E22">
+            <v>0.99165321729858402</v>
+          </cell>
+          <cell r="F22">
+            <v>-8.9656101168417103E-4</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>-5100</v>
+          </cell>
+          <cell r="D23">
+            <v>-3.0434256234177499E-3</v>
+          </cell>
+          <cell r="E23">
+            <v>0.99017417304629296</v>
+          </cell>
+          <cell r="F23">
+            <v>3.0776962678815399E-3</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>-18400</v>
+          </cell>
+          <cell r="D24">
+            <v>-2.9305775418053599E-3</v>
+          </cell>
+          <cell r="E24">
+            <v>0.992986662446251</v>
+          </cell>
+          <cell r="F24">
+            <v>3.0787657958864499E-3</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>3000</v>
+          </cell>
+          <cell r="D25">
+            <v>3.5324539794236898E-3</v>
+          </cell>
+          <cell r="E25">
+            <v>0.98223557898921099</v>
+          </cell>
+          <cell r="F25">
+            <v>-4.6952727690963703E-3</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>-9000</v>
+          </cell>
+          <cell r="D26">
+            <v>-3.8198372283031398E-3</v>
+          </cell>
+          <cell r="E26">
+            <v>0.99161772761015199</v>
+          </cell>
+          <cell r="F26">
+            <v>3.5105583022494199E-3</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>-12000</v>
+          </cell>
+          <cell r="D27">
+            <v>-3.8401717014692098E-3</v>
+          </cell>
+          <cell r="E27">
+            <v>0.99251199708402804</v>
+          </cell>
+          <cell r="F27">
+            <v>1.94843331581862E-3</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>-10400</v>
+          </cell>
+          <cell r="D28">
+            <v>-4.2082368273185199E-3</v>
+          </cell>
+          <cell r="E28">
+            <v>0.99195342477797199</v>
+          </cell>
+          <cell r="F28">
+            <v>2.54959487698086E-3</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>-25400</v>
+          </cell>
+          <cell r="D29">
+            <v>-4.7917371921926098E-3</v>
+          </cell>
+          <cell r="E29">
+            <v>0.99313747384920903</v>
+          </cell>
+          <cell r="F29">
+            <v>3.1356004368674399E-3</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>1200</v>
+          </cell>
+          <cell r="D30">
+            <v>7.8905722726396699E-4</v>
+          </cell>
+          <cell r="E30">
+            <v>0.98657251135836399</v>
+          </cell>
+          <cell r="F30">
+            <v>5.0453275062578497E-4</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>-10900</v>
+          </cell>
+          <cell r="D31">
+            <v>-4.3742107403335001E-3</v>
+          </cell>
+          <cell r="E31">
+            <v>0.99227775635904303</v>
+          </cell>
+          <cell r="F31">
+            <v>2.18397480503174E-3</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>3700</v>
+          </cell>
+          <cell r="D32">
+            <v>2.73144053143314E-3</v>
+          </cell>
+          <cell r="E32">
+            <v>0.98468075499298902</v>
+          </cell>
+          <cell r="F32">
+            <v>-3.6582652465511002E-4</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>300</v>
+          </cell>
+          <cell r="D33">
+            <v>3.7125561402706598E-4</v>
+          </cell>
+          <cell r="E33">
+            <v>0.98758988906408895</v>
+          </cell>
+          <cell r="F33">
+            <v>-8.77236162429073E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="4">
+          <cell r="C4">
+            <v>-30000</v>
+          </cell>
+          <cell r="D4">
+            <v>-7.1005114219915202E-3</v>
+          </cell>
+          <cell r="E4">
+            <v>0.98687155331839105</v>
+          </cell>
+          <cell r="F4">
+            <v>3.8523055154125602E-3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>-17700</v>
+          </cell>
+          <cell r="D5">
+            <v>-5.4879915948779501E-3</v>
+          </cell>
+          <cell r="E5">
+            <v>0.98579873248671801</v>
+          </cell>
+          <cell r="F5">
+            <v>8.9255436327625205E-3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>-2400</v>
+          </cell>
+          <cell r="D6">
+            <v>-1.8891290528479899E-3</v>
+          </cell>
+          <cell r="E6">
+            <v>0.97735059353243803</v>
+          </cell>
+          <cell r="F6">
+            <v>1.2864690327620801E-3</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>-16200</v>
+          </cell>
+          <cell r="D7">
+            <v>-4.6902020486753702E-3</v>
+          </cell>
+          <cell r="E7">
+            <v>0.98597451085221299</v>
+          </cell>
+          <cell r="F7">
+            <v>3.5789596609926899E-3</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>-4100</v>
+          </cell>
+          <cell r="D8">
+            <v>-3.10825963985383E-3</v>
+          </cell>
+          <cell r="E8">
+            <v>0.97854368409197801</v>
+          </cell>
+          <cell r="F8">
+            <v>2.86906274243881E-3</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>-3800</v>
+          </cell>
+          <cell r="D9">
+            <v>-2.8284535015579101E-3</v>
+          </cell>
+          <cell r="E9">
+            <v>0.979520853950544</v>
+          </cell>
+          <cell r="F9">
+            <v>1.8742756194701799E-3</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>-14800</v>
+          </cell>
+          <cell r="D10">
+            <v>-3.3681664511675999E-3</v>
+          </cell>
+          <cell r="E10">
+            <v>0.98598186336716298</v>
+          </cell>
+          <cell r="F10">
+            <v>7.5921083603877797E-3</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>-15600</v>
+          </cell>
+          <cell r="D11">
+            <v>-4.1848665397362598E-3</v>
+          </cell>
+          <cell r="E11">
+            <v>0.98546403612413302</v>
+          </cell>
+          <cell r="F11">
+            <v>2.8288248501487602E-3</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>-27800</v>
+          </cell>
+          <cell r="D12">
+            <v>-5.1077269464414E-3</v>
+          </cell>
+          <cell r="E12">
+            <v>0.986384223563469</v>
+          </cell>
+          <cell r="F12">
+            <v>2.0039067560449998E-3</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>-2200</v>
+          </cell>
+          <cell r="D13">
+            <v>-1.8933016596676599E-3</v>
+          </cell>
+          <cell r="E13">
+            <v>0.97556672042509296</v>
+          </cell>
+          <cell r="F13">
+            <v>1.802300296295E-3</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>-30000</v>
+          </cell>
+          <cell r="D14">
+            <v>-7.3447463576227806E-2</v>
+          </cell>
+          <cell r="E14">
+            <v>0.98666317701710105</v>
+          </cell>
+          <cell r="F14">
+            <v>0.50826848387610402</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>-16100</v>
+          </cell>
+          <cell r="D15">
+            <v>-5.6860264373161896E-3</v>
+          </cell>
+          <cell r="E15">
+            <v>0.98553140775509995</v>
+          </cell>
+          <cell r="F15">
+            <v>4.5363711615490302E-3</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>-800</v>
+          </cell>
+          <cell r="D16">
+            <v>-7.92087501608862E-4</v>
+          </cell>
+          <cell r="E16">
+            <v>0.96873515537362598</v>
+          </cell>
+          <cell r="F16">
+            <v>1.05064870934321E-3</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>-4600</v>
+          </cell>
+          <cell r="D17">
+            <v>-2.3925748875110999E-3</v>
+          </cell>
+          <cell r="E17">
+            <v>0.98081352989975901</v>
+          </cell>
+          <cell r="F17">
+            <v>1.0440257767501101E-3</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>-13500</v>
+          </cell>
+          <cell r="D18">
+            <v>-2.3779427084098099E-2</v>
+          </cell>
+          <cell r="E18">
+            <v>0.98507853086083097</v>
+          </cell>
+          <cell r="F18">
+            <v>0.274448081519169</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>-30000</v>
+          </cell>
+          <cell r="D19">
+            <v>-4.2948581326374198E-2</v>
+          </cell>
+          <cell r="E19">
+            <v>0.98669203928044902</v>
+          </cell>
+          <cell r="F19">
+            <v>0.38361754664286202</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>-1500</v>
+          </cell>
+          <cell r="D20">
+            <v>-1.0620422042069699E-3</v>
+          </cell>
+          <cell r="E20">
+            <v>0.976639431107304</v>
+          </cell>
+          <cell r="F20">
+            <v>-1.0786007040664001E-4</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>-25200</v>
+          </cell>
+          <cell r="D21">
+            <v>-4.0581164968855298E-3</v>
+          </cell>
+          <cell r="E21">
+            <v>0.98632371930376905</v>
+          </cell>
+          <cell r="F21">
+            <v>3.04817507616511E-3</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>-29500</v>
+          </cell>
+          <cell r="D22">
+            <v>-5.6729732591684302E-3</v>
+          </cell>
+          <cell r="E22">
+            <v>0.986860918191374</v>
+          </cell>
+          <cell r="F22">
+            <v>4.1940976844343503E-3</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>-11100</v>
+          </cell>
+          <cell r="D23">
+            <v>-4.5785567141622902E-3</v>
+          </cell>
+          <cell r="E23">
+            <v>0.98454058784881304</v>
+          </cell>
+          <cell r="F23">
+            <v>7.1211896071660097E-4</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>-4100</v>
+          </cell>
+          <cell r="D24">
+            <v>-3.13640204964787E-3</v>
+          </cell>
+          <cell r="E24">
+            <v>0.97953468927992304</v>
+          </cell>
+          <cell r="F24">
+            <v>6.6526545502562798E-3</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>-3900</v>
+          </cell>
+          <cell r="D25">
+            <v>-2.3964308390415001E-3</v>
+          </cell>
+          <cell r="E25">
+            <v>0.97640748133719102</v>
+          </cell>
+          <cell r="F25">
+            <v>5.1954422990063698E-4</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>-4200</v>
+          </cell>
+          <cell r="D26">
+            <v>-2.5513668168103899E-3</v>
+          </cell>
+          <cell r="E26">
+            <v>0.97909581751281904</v>
+          </cell>
+          <cell r="F26">
+            <v>1.81615678061086E-3</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>-1500</v>
+          </cell>
+          <cell r="D27">
+            <v>-1.1126125378509899E-3</v>
+          </cell>
+          <cell r="E27">
+            <v>0.97372841250838005</v>
+          </cell>
+          <cell r="F27">
+            <v>-5.6107163235391501E-4</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>-200</v>
+          </cell>
+          <cell r="D28">
+            <v>-2.9951742651201902E-4</v>
+          </cell>
+          <cell r="E28">
+            <v>0.96836763272662596</v>
+          </cell>
+          <cell r="F28">
+            <v>4.78926633556022E-4</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>-30000</v>
+          </cell>
+          <cell r="D29">
+            <v>-4.8248103643004896E-3</v>
+          </cell>
+          <cell r="E29">
+            <v>0.98679324775298705</v>
+          </cell>
+          <cell r="F29">
+            <v>2.8284088861917299E-3</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>-6000</v>
+          </cell>
+          <cell r="D30">
+            <v>-3.3132330134734698E-3</v>
+          </cell>
+          <cell r="E30">
+            <v>0.98111511541982899</v>
+          </cell>
+          <cell r="F30">
+            <v>3.7980373392806901E-3</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>-1400</v>
+          </cell>
+          <cell r="D31">
+            <v>-1.4380928700846701E-3</v>
+          </cell>
+          <cell r="E31">
+            <v>0.97149092470559695</v>
+          </cell>
+          <cell r="F31">
+            <v>8.1718573538280804E-4</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>-3100</v>
+          </cell>
+          <cell r="D32">
+            <v>-2.26853149136163E-3</v>
+          </cell>
+          <cell r="E32">
+            <v>0.97704650283188599</v>
+          </cell>
+          <cell r="F32">
+            <v>3.2910026702049301E-3</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>-30000</v>
+          </cell>
+          <cell r="D33">
+            <v>-6.2606415771508297E-3</v>
+          </cell>
+          <cell r="E33">
+            <v>0.98681963302432996</v>
+          </cell>
+          <cell r="F33">
+            <v>5.6122652139269204E-3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="4">
+          <cell r="C4">
+            <v>1700</v>
+          </cell>
+          <cell r="D4">
+            <v>1.10062282759337E-3</v>
+          </cell>
+          <cell r="E4">
+            <v>0.98498031908060801</v>
+          </cell>
+          <cell r="F4">
+            <v>-2.2807006902435499E-3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>-4600</v>
+          </cell>
+          <cell r="D5">
+            <v>-1.8682626770695199E-3</v>
+          </cell>
+          <cell r="E5">
+            <v>0.99410766359835101</v>
+          </cell>
+          <cell r="F5">
+            <v>1.8337801287048199E-3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>-1700</v>
+          </cell>
+          <cell r="D6">
+            <v>-1.3305552251365799E-3</v>
+          </cell>
+          <cell r="E6">
+            <v>0.99145550077572098</v>
+          </cell>
+          <cell r="F6">
+            <v>1.70843410751445E-3</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>-100</v>
+          </cell>
+          <cell r="D7">
+            <v>-2.2011977947045099E-6</v>
+          </cell>
+          <cell r="E7">
+            <v>0.99099183649543698</v>
+          </cell>
+          <cell r="F7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>1400</v>
+          </cell>
+          <cell r="D8">
+            <v>6.1508165837997897E-4</v>
+          </cell>
+          <cell r="E8">
+            <v>0.98729959009771395</v>
+          </cell>
+          <cell r="F8">
+            <v>-1.9512732532300699E-4</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>1200</v>
+          </cell>
+          <cell r="D9">
+            <v>1.01901495740119E-3</v>
+          </cell>
+          <cell r="E9">
+            <v>0.98937507436105898</v>
+          </cell>
+          <cell r="F9">
+            <v>2.2421997582870098E-3</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>-6700</v>
+          </cell>
+          <cell r="D10">
+            <v>-2.5244220974957E-3</v>
+          </cell>
+          <cell r="E10">
+            <v>0.99386890014441398</v>
+          </cell>
+          <cell r="F10">
+            <v>2.7931703548921801E-3</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>2500</v>
+          </cell>
+          <cell r="D11">
+            <v>2.1026853766409298E-3</v>
+          </cell>
+          <cell r="E11">
+            <v>0.98639010635010405</v>
+          </cell>
+          <cell r="F11">
+            <v>-3.9834054963709599E-4</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>-20700</v>
+          </cell>
+          <cell r="D12">
+            <v>-3.40908384484506E-3</v>
+          </cell>
+          <cell r="E12">
+            <v>0.99680188209300302</v>
+          </cell>
+          <cell r="F12">
+            <v>3.4601407434816898E-3</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>3200</v>
+          </cell>
+          <cell r="D13">
+            <v>3.0972900504867501E-3</v>
+          </cell>
+          <cell r="E13">
+            <v>0.98249128723226997</v>
+          </cell>
+          <cell r="F13">
+            <v>9.0711773134788398E-4</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>6300</v>
+          </cell>
+          <cell r="D14">
+            <v>6.24249992858005E-3</v>
+          </cell>
+          <cell r="E14">
+            <v>0.97726358451110196</v>
+          </cell>
+          <cell r="F14">
+            <v>-7.5750863865021497E-3</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>-6400</v>
+          </cell>
+          <cell r="D15">
+            <v>-2.4320736288213599E-3</v>
+          </cell>
+          <cell r="E15">
+            <v>0.99480255485563795</v>
+          </cell>
+          <cell r="F15">
+            <v>4.3150980055167397E-3</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>400</v>
+          </cell>
+          <cell r="D16">
+            <v>4.7237857292325899E-4</v>
+          </cell>
+          <cell r="E16">
+            <v>0.98558242516106298</v>
+          </cell>
+          <cell r="F16">
+            <v>1.12457626755606E-3</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>3000</v>
+          </cell>
+          <cell r="D17">
+            <v>2.3982117002102599E-3</v>
+          </cell>
+          <cell r="E17">
+            <v>0.98718614132654203</v>
+          </cell>
+          <cell r="F17">
+            <v>-3.7266454008523702E-3</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>-10500</v>
+          </cell>
+          <cell r="D18">
+            <v>-2.88682682867724E-3</v>
+          </cell>
+          <cell r="E18">
+            <v>0.99553218232955099</v>
+          </cell>
+          <cell r="F18">
+            <v>2.0184466823093901E-3</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>800</v>
+          </cell>
+          <cell r="D19">
+            <v>3.4266313059327902E-4</v>
+          </cell>
+          <cell r="E19">
+            <v>0.98981546539506804</v>
+          </cell>
+          <cell r="F19">
+            <v>-2.9035944088125001E-3</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>2400</v>
+          </cell>
+          <cell r="D20">
+            <v>1.3824407409433999E-3</v>
+          </cell>
+          <cell r="E20">
+            <v>0.98838050046119297</v>
+          </cell>
+          <cell r="F20">
+            <v>-5.8757895288296998E-3</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>-30000</v>
+          </cell>
+          <cell r="D21">
+            <v>-4.0576147848414498E-3</v>
+          </cell>
+          <cell r="E21">
+            <v>0.996906541464464</v>
+          </cell>
+          <cell r="F21">
+            <v>5.8036199420665102E-3</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>200</v>
+          </cell>
+          <cell r="D22">
+            <v>1.7546933284751001E-4</v>
+          </cell>
+          <cell r="E22">
+            <v>0.98876113016338896</v>
+          </cell>
+          <cell r="F22">
+            <v>-1.21371351810894E-4</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>-30000</v>
+          </cell>
+          <cell r="D23">
+            <v>-3.4322651013068898E-3</v>
+          </cell>
+          <cell r="E23">
+            <v>0.99677839063895401</v>
+          </cell>
+          <cell r="F23">
+            <v>1.0280245421169E-3</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>-2900</v>
+          </cell>
+          <cell r="D24">
+            <v>-1.3586660044009301E-3</v>
+          </cell>
+          <cell r="E24">
+            <v>0.99422898897900303</v>
+          </cell>
+          <cell r="F24">
+            <v>2.3265224199887002E-3</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>2500</v>
+          </cell>
+          <cell r="D25">
+            <v>1.89126608855683E-3</v>
+          </cell>
+          <cell r="E25">
+            <v>0.98640025559979905</v>
+          </cell>
+          <cell r="F25">
+            <v>-5.3253045064557102E-3</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>11900</v>
+          </cell>
+          <cell r="D26">
+            <v>7.7068485576757897E-2</v>
+          </cell>
+          <cell r="E26">
+            <v>0.84076958932432599</v>
+          </cell>
+          <cell r="F26">
+            <v>-0.13072853269083401</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>-13300</v>
+          </cell>
+          <cell r="D27">
+            <v>-2.4912901446911802E-3</v>
+          </cell>
+          <cell r="E27">
+            <v>0.99628767808610896</v>
+          </cell>
+          <cell r="F27">
+            <v>1.1887513924489701E-3</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>4000</v>
+          </cell>
+          <cell r="D28">
+            <v>4.6374909079507304E-3</v>
+          </cell>
+          <cell r="E28">
+            <v>0.98177786701081304</v>
+          </cell>
+          <cell r="F28">
+            <v>-4.8468769372609901E-3</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>-1000</v>
+          </cell>
+          <cell r="D29">
+            <v>-3.3591600618099101E-4</v>
+          </cell>
+          <cell r="E29">
+            <v>0.99071389524438003</v>
+          </cell>
+          <cell r="F29">
+            <v>6.1630899999999501E-4</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>1300</v>
+          </cell>
+          <cell r="D30">
+            <v>1.3382220779893899E-3</v>
+          </cell>
+          <cell r="E30">
+            <v>0.98739408624553304</v>
+          </cell>
+          <cell r="F30">
+            <v>-1.44404672564077E-3</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>-4500</v>
+          </cell>
+          <cell r="D31">
+            <v>-1.9885325852708698E-3</v>
+          </cell>
+          <cell r="E31">
+            <v>0.993324506956071</v>
+          </cell>
+          <cell r="F31">
+            <v>-2.7000402398105099E-3</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>-3700</v>
+          </cell>
+          <cell r="D32">
+            <v>-2.1781471561135302E-3</v>
+          </cell>
+          <cell r="E32">
+            <v>0.99336681265598203</v>
+          </cell>
+          <cell r="F32">
+            <v>2.4655135084373698E-3</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>-17900</v>
+          </cell>
+          <cell r="D33">
+            <v>-4.8503293867775401E-3</v>
+          </cell>
+          <cell r="E33">
+            <v>0.99628966584027501</v>
+          </cell>
+          <cell r="F33">
+            <v>3.9909273234590903E-3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="4">
+          <cell r="C4">
+            <v>-16800</v>
+          </cell>
+          <cell r="D4">
+            <v>-2.46040863859345E-2</v>
+          </cell>
+          <cell r="E4">
+            <v>0.99305951033994899</v>
+          </cell>
+          <cell r="F4">
+            <v>0.12641769222756899</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>-21100</v>
+          </cell>
+          <cell r="D5">
+            <v>-5.6539851438034902E-2</v>
+          </cell>
+          <cell r="E5">
+            <v>0.99313187557622695</v>
+          </cell>
+          <cell r="F5">
+            <v>0.23609067374838499</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>9200</v>
+          </cell>
+          <cell r="D6">
+            <v>0.25823141624381502</v>
+          </cell>
+          <cell r="E6">
+            <v>0.59149476181650895</v>
+          </cell>
+          <cell r="F6">
+            <v>-0.27580101308231197</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>4900</v>
+          </cell>
+          <cell r="D7">
+            <v>0.15892121131306</v>
+          </cell>
+          <cell r="E7">
+            <v>0.75114364631868902</v>
+          </cell>
+          <cell r="F7">
+            <v>-0.399486082564184</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>-30000</v>
+          </cell>
+          <cell r="D8">
+            <v>-6.4048379248984502E-2</v>
+          </cell>
+          <cell r="E8">
+            <v>0.99255692479317403</v>
+          </cell>
+          <cell r="F8">
+            <v>0.24845030235641</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>-25600</v>
+          </cell>
+          <cell r="D9">
+            <v>-4.1211512526129E-2</v>
+          </cell>
+          <cell r="E9">
+            <v>0.99136565591953996</v>
+          </cell>
+          <cell r="F9">
+            <v>0.18877196182539999</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>-30000</v>
+          </cell>
+          <cell r="D10">
+            <v>-4.9252859797359001E-2</v>
+          </cell>
+          <cell r="E10">
+            <v>0.98992995483894797</v>
+          </cell>
+          <cell r="F10">
+            <v>7.9895529873842699E-2</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>-30000</v>
+          </cell>
+          <cell r="D11">
+            <v>-1.6298722760565602E-2</v>
+          </cell>
+          <cell r="E11">
+            <v>0.99257127374168896</v>
+          </cell>
+          <cell r="F11">
+            <v>7.0897684882383197E-2</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>5400</v>
+          </cell>
+          <cell r="D12">
+            <v>0.14877240706314801</v>
+          </cell>
+          <cell r="E12">
+            <v>0.72587443673245999</v>
+          </cell>
+          <cell r="F12">
+            <v>-0.30976012065077302</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>-20000</v>
+          </cell>
+          <cell r="D13">
+            <v>-6.8569575540215998E-3</v>
+          </cell>
+          <cell r="E13">
+            <v>0.99228127130060695</v>
+          </cell>
+          <cell r="F13">
+            <v>6.6116976577093303E-3</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>-16600</v>
+          </cell>
+          <cell r="D14">
+            <v>-3.68892179374255E-2</v>
+          </cell>
+          <cell r="E14">
+            <v>0.99200530035275203</v>
+          </cell>
+          <cell r="F14">
+            <v>0.180635135401638</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>-17500</v>
+          </cell>
+          <cell r="D15">
+            <v>-1.8856975995758401E-2</v>
+          </cell>
+          <cell r="E15">
+            <v>0.98549109730248896</v>
+          </cell>
+          <cell r="F15">
+            <v>4.44655507247637E-2</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>-26800</v>
+          </cell>
+          <cell r="D16">
+            <v>-7.4399828343244406E-2</v>
+          </cell>
+          <cell r="E16">
+            <v>0.991932123006811</v>
+          </cell>
+          <cell r="F16">
+            <v>0.261077185217644</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>-15700</v>
+          </cell>
+          <cell r="D17">
+            <v>-3.3520974027362802E-2</v>
+          </cell>
+          <cell r="E17">
+            <v>0.99169990260343299</v>
+          </cell>
+          <cell r="F17">
+            <v>0.16608733095460099</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>9100</v>
+          </cell>
+          <cell r="D18">
+            <v>0.64440137058182201</v>
+          </cell>
+          <cell r="E18">
+            <v>0</v>
+          </cell>
+          <cell r="F18">
+            <v>-1.239270585741</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>-23100</v>
+          </cell>
+          <cell r="D19">
+            <v>-6.9215951301341602E-2</v>
+          </cell>
+          <cell r="E19">
+            <v>0.99027791826801703</v>
+          </cell>
+          <cell r="F19">
+            <v>0.240466646099638</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>-22200</v>
+          </cell>
+          <cell r="D20">
+            <v>-1.9169226401721199E-2</v>
+          </cell>
+          <cell r="E20">
+            <v>0.989468665376662</v>
+          </cell>
+          <cell r="F20">
+            <v>6.4365504239146498E-2</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>-19100</v>
+          </cell>
+          <cell r="D21">
+            <v>-9.0516222899134496E-2</v>
+          </cell>
+          <cell r="E21">
+            <v>0.991168831967845</v>
+          </cell>
+          <cell r="F21">
+            <v>0.28987547304325401</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>-30000</v>
+          </cell>
+          <cell r="D22">
+            <v>-7.0595868443763296E-2</v>
+          </cell>
+          <cell r="E22">
+            <v>0.989134331332716</v>
+          </cell>
+          <cell r="F22">
+            <v>0.26564846897187799</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>-30000</v>
+          </cell>
+          <cell r="D23">
+            <v>-3.1482506527532102E-2</v>
+          </cell>
+          <cell r="E23">
+            <v>0.99190561706295599</v>
+          </cell>
+          <cell r="F23">
+            <v>0.16570935656639399</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>-21800</v>
+          </cell>
+          <cell r="D24">
+            <v>-3.8049855009986901E-2</v>
+          </cell>
+          <cell r="E24">
+            <v>0.99234622806797801</v>
+          </cell>
+          <cell r="F24">
+            <v>0.144188608602076</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>-14500</v>
+          </cell>
+          <cell r="D25">
+            <v>-4.03969872150566E-2</v>
+          </cell>
+          <cell r="E25">
+            <v>0.98829670614082599</v>
+          </cell>
+          <cell r="F25">
+            <v>0.18894053716050599</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>-15100</v>
+          </cell>
+          <cell r="D26">
+            <v>-6.7164268112700903E-2</v>
+          </cell>
+          <cell r="E26">
+            <v>0.98469243532290995</v>
+          </cell>
+          <cell r="F26">
+            <v>0.247010951439184</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>-12900</v>
+          </cell>
+          <cell r="D27">
+            <v>-5.5051693013052896E-3</v>
+          </cell>
+          <cell r="E27">
+            <v>0.99095122113672096</v>
+          </cell>
+          <cell r="F27">
+            <v>2.5186997760617402E-2</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>-30000</v>
+          </cell>
+          <cell r="D28">
+            <v>-1.23863529174089E-2</v>
+          </cell>
+          <cell r="E28">
+            <v>0.99138221882092203</v>
+          </cell>
+          <cell r="F28">
+            <v>7.2015658468263299E-2</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>-15600</v>
+          </cell>
+          <cell r="D29">
+            <v>-7.5939556705665198E-2</v>
+          </cell>
+          <cell r="E29">
+            <v>0.99060346178450098</v>
+          </cell>
+          <cell r="F29">
+            <v>0.279743046920302</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>-20000</v>
+          </cell>
+          <cell r="D30">
+            <v>-3.1367822205633999E-2</v>
+          </cell>
+          <cell r="E30">
+            <v>0.99119940309557297</v>
+          </cell>
+          <cell r="F30">
+            <v>0.16603459692549499</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>-20800</v>
+          </cell>
+          <cell r="D31">
+            <v>-9.0684865102678095E-3</v>
+          </cell>
+          <cell r="E31">
+            <v>0.99238152090076204</v>
+          </cell>
+          <cell r="F31">
+            <v>9.9101011393004593E-3</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>-7500</v>
+          </cell>
+          <cell r="D32">
+            <v>-3.7532747765807099E-3</v>
+          </cell>
+          <cell r="E32">
+            <v>0.98581771044636701</v>
+          </cell>
+          <cell r="F32">
+            <v>1.23126229692725E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>-30000</v>
+          </cell>
+          <cell r="D33">
+            <v>-7.8452871782437705E-2</v>
+          </cell>
+          <cell r="E33">
+            <v>0.98715881117719595</v>
+          </cell>
+          <cell r="F33">
+            <v>0.27668192501396599</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5">
+        <row r="4">
+          <cell r="C4">
+            <v>9200</v>
+          </cell>
+          <cell r="D4">
+            <v>-3.7235653433450502E-3</v>
+          </cell>
+          <cell r="E4">
+            <v>0.87071135422721302</v>
+          </cell>
+          <cell r="F4">
+            <v>2.41894361971228E-3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>6900</v>
+          </cell>
+          <cell r="D5">
+            <v>-2.0545710363301101E-4</v>
+          </cell>
+          <cell r="E5">
+            <v>0.86860084464737697</v>
+          </cell>
+          <cell r="F5">
+            <v>9.4184950611304608E-3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>3000</v>
+          </cell>
+          <cell r="D6">
+            <v>-6.2227242417824402E-3</v>
+          </cell>
+          <cell r="E6">
+            <v>0.86624566698435401</v>
+          </cell>
+          <cell r="F6">
+            <v>7.4072554880356602E-3</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>10500</v>
+          </cell>
+          <cell r="D7">
+            <v>2.0805972147597199E-5</v>
+          </cell>
+          <cell r="E7">
+            <v>0.86403634964148501</v>
+          </cell>
+          <cell r="F7">
+            <v>9.6830525324004199E-3</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>21500</v>
+          </cell>
+          <cell r="D8">
+            <v>1.26433414574819E-2</v>
+          </cell>
+          <cell r="E8">
+            <v>0.83788354543462096</v>
+          </cell>
+          <cell r="F8">
+            <v>-6.2258725178009301E-3</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>19500</v>
+          </cell>
+          <cell r="D9">
+            <v>2.2404850755418601E-3</v>
+          </cell>
+          <cell r="E9">
+            <v>0.86139566914017596</v>
+          </cell>
+          <cell r="F9">
+            <v>1.0912163952796899E-2</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>16700</v>
+          </cell>
+          <cell r="D10">
+            <v>3.0823888403102E-3</v>
+          </cell>
+          <cell r="E10">
+            <v>0.86498941429850196</v>
+          </cell>
+          <cell r="F10">
+            <v>-1.1476083954315999E-2</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>9900</v>
+          </cell>
+          <cell r="D11">
+            <v>5.4428339900058898E-4</v>
+          </cell>
+          <cell r="E11">
+            <v>0.86385585727967296</v>
+          </cell>
+          <cell r="F11">
+            <v>-2.7941881277670701E-2</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>19600</v>
+          </cell>
+          <cell r="D12">
+            <v>7.2352758942236198E-3</v>
+          </cell>
+          <cell r="E12">
+            <v>0.84615167265581803</v>
+          </cell>
+          <cell r="F12">
+            <v>1.28330925438553E-2</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>11800</v>
+          </cell>
+          <cell r="D13">
+            <v>7.1349637395395904E-4</v>
+          </cell>
+          <cell r="E13">
+            <v>0.86422468165129496</v>
+          </cell>
+          <cell r="F13">
+            <v>1.6348332850218101E-2</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>20900</v>
+          </cell>
+          <cell r="D14">
+            <v>1.0416582365792499E-2</v>
+          </cell>
+          <cell r="E14">
+            <v>0.84226358676789603</v>
+          </cell>
+          <cell r="F14">
+            <v>3.7285562679005798E-3</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>20000</v>
+          </cell>
+          <cell r="D15">
+            <v>5.5337380348247003E-3</v>
+          </cell>
+          <cell r="E15">
+            <v>0.85918414934673504</v>
+          </cell>
+          <cell r="F15">
+            <v>6.4685116879062898E-3</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>12600</v>
+          </cell>
+          <cell r="D16">
+            <v>4.6780539510161102E-3</v>
+          </cell>
+          <cell r="E16">
+            <v>0.85024008327223699</v>
+          </cell>
+          <cell r="F16">
+            <v>-1.78977973209437E-3</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>15200</v>
+          </cell>
+          <cell r="D17">
+            <v>6.0935091239663897E-3</v>
+          </cell>
+          <cell r="E17">
+            <v>0.85812572812420895</v>
+          </cell>
+          <cell r="F17">
+            <v>-1.37761608985909E-2</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>21700</v>
+          </cell>
+          <cell r="D18">
+            <v>8.5132854523294298E-3</v>
+          </cell>
+          <cell r="E18">
+            <v>0.85095197382863796</v>
+          </cell>
+          <cell r="F18">
+            <v>-1.21767550640211E-3</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>21300</v>
+          </cell>
+          <cell r="D19">
+            <v>1.0923536398642301E-2</v>
+          </cell>
+          <cell r="E19">
+            <v>0.84747971128060995</v>
+          </cell>
+          <cell r="F19">
+            <v>-2.0207482958943802E-2</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>15600</v>
+          </cell>
+          <cell r="D20">
+            <v>-2.70887456100765E-4</v>
+          </cell>
+          <cell r="E20">
+            <v>0.86418508361846602</v>
+          </cell>
+          <cell r="F20">
+            <v>-6.11859052617087E-3</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>14600</v>
+          </cell>
+          <cell r="D21">
+            <v>2.70464826175947E-3</v>
+          </cell>
+          <cell r="E21">
+            <v>0.86211790980985603</v>
+          </cell>
+          <cell r="F21">
+            <v>4.13129728437366E-3</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>16600</v>
+          </cell>
+          <cell r="D22">
+            <v>2.2632684825585301E-4</v>
+          </cell>
+          <cell r="E22">
+            <v>0.86644542592687701</v>
+          </cell>
+          <cell r="F22">
+            <v>1.11314132588568E-2</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>20300</v>
+          </cell>
+          <cell r="D23">
+            <v>1.30419989450693E-2</v>
+          </cell>
+          <cell r="E23">
+            <v>0.84676399992794404</v>
+          </cell>
+          <cell r="F23">
+            <v>2.2537277481197299E-3</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>7800</v>
+          </cell>
+          <cell r="D24">
+            <v>5.2290617415873203E-3</v>
+          </cell>
+          <cell r="E24">
+            <v>0.856126644676657</v>
+          </cell>
+          <cell r="F24">
+            <v>1.6605586224087399E-3</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>20900</v>
+          </cell>
+          <cell r="D25">
+            <v>1.1960004827523099E-3</v>
+          </cell>
+          <cell r="E25">
+            <v>0.86109967750270899</v>
+          </cell>
+          <cell r="F25">
+            <v>-2.20356715835778E-2</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>17000</v>
+          </cell>
+          <cell r="D26">
+            <v>1.19818840894125E-4</v>
+          </cell>
+          <cell r="E26">
+            <v>0.86024324146904996</v>
+          </cell>
+          <cell r="F26">
+            <v>-6.1286501968491596E-3</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>22700</v>
+          </cell>
+          <cell r="D27">
+            <v>1.25043624186073E-2</v>
+          </cell>
+          <cell r="E27">
+            <v>0.83941323609356899</v>
+          </cell>
+          <cell r="F27">
+            <v>-2.04225772857256E-2</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>19300</v>
+          </cell>
+          <cell r="D28">
+            <v>1.58962639783943E-3</v>
+          </cell>
+          <cell r="E28">
+            <v>0.85984177395962602</v>
+          </cell>
+          <cell r="F28">
+            <v>-4.5254116492518398E-3</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>4600</v>
+          </cell>
+          <cell r="D29">
+            <v>2.68526963252241E-3</v>
+          </cell>
+          <cell r="E29">
+            <v>0.86407616786074104</v>
+          </cell>
+          <cell r="F29">
+            <v>-8.6370126225220299E-3</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>21700</v>
+          </cell>
+          <cell r="D30">
+            <v>1.46426512386493E-3</v>
+          </cell>
+          <cell r="E30">
+            <v>0.85902557512046096</v>
+          </cell>
+          <cell r="F30">
+            <v>1.0620176477237301E-3</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>12400</v>
+          </cell>
+          <cell r="D31">
+            <v>5.20327574474871E-3</v>
+          </cell>
+          <cell r="E31">
+            <v>0.85511105894828798</v>
+          </cell>
+          <cell r="F31">
+            <v>9.0254622444018301E-3</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>19800</v>
+          </cell>
+          <cell r="D32">
+            <v>6.5749714132197698E-3</v>
+          </cell>
+          <cell r="E32">
+            <v>0.84942842727967005</v>
+          </cell>
+          <cell r="F32">
+            <v>-1.76621808816891E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>1600</v>
+          </cell>
+          <cell r="D33">
+            <v>6.3584868398214301E-4</v>
+          </cell>
+          <cell r="E33">
+            <v>0.86534157076564799</v>
+          </cell>
+          <cell r="F33">
+            <v>-1.37904708023407E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6">
+        <row r="4">
+          <cell r="C4">
+            <v>11100</v>
+          </cell>
+          <cell r="D4">
+            <v>2.10658847006324E-3</v>
+          </cell>
+          <cell r="E4">
+            <v>0.94684976264012199</v>
+          </cell>
+          <cell r="F4">
+            <v>-5.2242760335330296E-3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>-21900</v>
+          </cell>
+          <cell r="D5">
+            <v>-5.8684472604744698E-4</v>
+          </cell>
+          <cell r="E5">
+            <v>0.97631221369139298</v>
+          </cell>
+          <cell r="F5">
+            <v>1.0109118381800199E-3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>11600</v>
+          </cell>
+          <cell r="D6">
+            <v>2.0930265203309901E-3</v>
+          </cell>
+          <cell r="E6">
+            <v>0.95237250241049098</v>
+          </cell>
+          <cell r="F6">
+            <v>-1.95846461746285E-3</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>12300</v>
+          </cell>
+          <cell r="D7">
+            <v>3.0809628333879702E-3</v>
+          </cell>
+          <cell r="E7">
+            <v>0.94431185566363396</v>
+          </cell>
+          <cell r="F7">
+            <v>-2.1328006759585498E-3</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>12400</v>
+          </cell>
+          <cell r="D8">
+            <v>4.3594652387582899E-3</v>
+          </cell>
+          <cell r="E8">
+            <v>0.92737796477991397</v>
+          </cell>
+          <cell r="F8">
+            <v>-6.5108424817733003E-3</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>11200</v>
+          </cell>
+          <cell r="D9">
+            <v>1.64544161179437E-3</v>
+          </cell>
+          <cell r="E9">
+            <v>0.95467302175826896</v>
+          </cell>
+          <cell r="F9">
+            <v>-3.42965240311388E-3</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>9800</v>
+          </cell>
+          <cell r="D10">
+            <v>1.70275215063259E-3</v>
+          </cell>
+          <cell r="E10">
+            <v>0.95838978149313603</v>
+          </cell>
+          <cell r="F10">
+            <v>-3.8742538803804801E-3</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>9300</v>
+          </cell>
+          <cell r="D11">
+            <v>1.40818298951674E-3</v>
+          </cell>
+          <cell r="E11">
+            <v>0.95833717634418003</v>
+          </cell>
+          <cell r="F11">
+            <v>-1.9166022357748301E-3</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>10700</v>
+          </cell>
+          <cell r="D12">
+            <v>1.90470563775468E-3</v>
+          </cell>
+          <cell r="E12">
+            <v>0.95181547376676501</v>
+          </cell>
+          <cell r="F12">
+            <v>-3.4359154587345602E-3</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>11200</v>
+          </cell>
+          <cell r="D13">
+            <v>1.4244886890251399E-3</v>
+          </cell>
+          <cell r="E13">
+            <v>0.95877056342024103</v>
+          </cell>
+          <cell r="F13">
+            <v>-2.16589126147676E-3</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>7000</v>
+          </cell>
+          <cell r="D14">
+            <v>4.4538697104159997E-4</v>
+          </cell>
+          <cell r="E14">
+            <v>0.97035495982734299</v>
+          </cell>
+          <cell r="F14">
+            <v>2.76360779528694E-3</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>-14400</v>
+          </cell>
+          <cell r="D15">
+            <v>-1.11601282585332E-4</v>
+          </cell>
+          <cell r="E15">
+            <v>0.97441072888179303</v>
+          </cell>
+          <cell r="F15">
+            <v>-7.4250580818913104E-4</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>-3600</v>
+          </cell>
+          <cell r="D16">
+            <v>-4.9144273220492996E-4</v>
+          </cell>
+          <cell r="E16">
+            <v>0.97657319814629195</v>
+          </cell>
+          <cell r="F16">
+            <v>2.2241594888672199E-4</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>7700</v>
+          </cell>
+          <cell r="D17">
+            <v>9.2596880348273704E-4</v>
+          </cell>
+          <cell r="E17">
+            <v>0.96544282738167597</v>
+          </cell>
+          <cell r="F17">
+            <v>-1.2316503781557499E-3</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>900</v>
+          </cell>
+          <cell r="D18">
+            <v>2.9509015628147102E-4</v>
+          </cell>
+          <cell r="E18">
+            <v>0.97125013148256001</v>
+          </cell>
+          <cell r="F18">
+            <v>-1.5274381637497801E-4</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19">
+            <v>9800</v>
+          </cell>
+          <cell r="D19">
+            <v>1.30626921906651E-3</v>
+          </cell>
+          <cell r="E19">
+            <v>0.95841603660946195</v>
+          </cell>
+          <cell r="F19">
+            <v>-2.28178988861293E-4</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20">
+            <v>7500</v>
+          </cell>
+          <cell r="D20">
+            <v>6.3425879394915497E-4</v>
+          </cell>
+          <cell r="E20">
+            <v>0.96630710902040395</v>
+          </cell>
+          <cell r="F20">
+            <v>-9.8763005355828604E-4</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21">
+            <v>600</v>
+          </cell>
+          <cell r="D21">
+            <v>1.6297981431992399E-4</v>
+          </cell>
+          <cell r="E21">
+            <v>0.96838992739061402</v>
+          </cell>
+          <cell r="F21">
+            <v>3.8852833327827001E-3</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22">
+            <v>9800</v>
+          </cell>
+          <cell r="D22">
+            <v>7.5451235957445196E-4</v>
+          </cell>
+          <cell r="E22">
+            <v>0.96459018710254696</v>
+          </cell>
+          <cell r="F22">
+            <v>-1.22004643815976E-3</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23">
+            <v>800</v>
+          </cell>
+          <cell r="D23">
+            <v>1.12959564144601E-4</v>
+          </cell>
+          <cell r="E23">
+            <v>0.97419068795572605</v>
+          </cell>
+          <cell r="F23">
+            <v>-8.5216287226152999E-4</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24">
+            <v>8200</v>
+          </cell>
+          <cell r="D24">
+            <v>1.22780953872404E-3</v>
+          </cell>
+          <cell r="E24">
+            <v>0.96201129939014096</v>
+          </cell>
+          <cell r="F24">
+            <v>-2.06096371513386E-3</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>-600</v>
+          </cell>
+          <cell r="D25">
+            <v>-2.8622446976743401E-4</v>
+          </cell>
+          <cell r="E25">
+            <v>0.97362628624103797</v>
+          </cell>
+          <cell r="F25">
+            <v>1.17100064228736E-3</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>400</v>
+          </cell>
+          <cell r="D26">
+            <v>1.10018913124398E-4</v>
+          </cell>
+          <cell r="E26">
+            <v>0.97038476035681498</v>
+          </cell>
+          <cell r="F26">
+            <v>-1.1917659954188101E-3</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>8300</v>
+          </cell>
+          <cell r="D27">
+            <v>9.4764022362116198E-4</v>
+          </cell>
+          <cell r="E27">
+            <v>0.96445304239985896</v>
+          </cell>
+          <cell r="F27">
+            <v>1.4803297169123E-3</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>12500</v>
+          </cell>
+          <cell r="D28">
+            <v>3.5562730782175401E-3</v>
+          </cell>
+          <cell r="E28">
+            <v>0.93279823229676195</v>
+          </cell>
+          <cell r="F28">
+            <v>-4.0789013558030201E-3</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>11000</v>
+          </cell>
+          <cell r="D29">
+            <v>1.32764202108005E-3</v>
+          </cell>
+          <cell r="E29">
+            <v>0.95731814513258096</v>
+          </cell>
+          <cell r="F29">
+            <v>-4.4142500700672301E-4</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>5000</v>
+          </cell>
+          <cell r="D30">
+            <v>3.7488475641708698E-4</v>
+          </cell>
+          <cell r="E30">
+            <v>0.97345082656368598</v>
+          </cell>
+          <cell r="F30">
+            <v>-1.2113950797222801E-3</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>12400</v>
+          </cell>
+          <cell r="D31">
+            <v>2.62787815931371E-3</v>
+          </cell>
+          <cell r="E31">
+            <v>0.94702258438312104</v>
+          </cell>
+          <cell r="F31">
+            <v>-2.2650228081930101E-3</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32">
+            <v>11400</v>
+          </cell>
+          <cell r="D32">
+            <v>1.75773465396693E-3</v>
+          </cell>
+          <cell r="E32">
+            <v>0.95539827117188703</v>
+          </cell>
+          <cell r="F32">
+            <v>9.65543453944617E-5</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33">
+            <v>-6200</v>
+          </cell>
+          <cell r="D33">
+            <v>1.87343264214642E-4</v>
+          </cell>
+          <cell r="E33">
+            <v>0.97212790422658701</v>
+          </cell>
+          <cell r="F33">
+            <v>6.8535011062809104E-4</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5840,7 +7835,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5875,7 +7870,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6052,16 +8047,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:V34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
@@ -6071,7 +8066,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -6085,7 +8080,7 @@
         <v>0.66616012487499998</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -6105,7 +8100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="4">
         <v>0</v>
       </c>
@@ -6125,7 +8120,7 @@
         <v>-8.1951611083141897E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -6145,7 +8140,7 @@
         <v>-3.6281739877806699E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -6165,7 +8160,7 @@
         <v>4.5989107833585502E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -6185,7 +8180,7 @@
         <v>-4.6405229793171797E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -6205,7 +8200,7 @@
         <v>-1.0926191401774399E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -6225,7 +8220,7 @@
         <v>-3.8592048051273001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -6245,7 +8240,7 @@
         <v>-5.2609140308685302E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>7</v>
       </c>
@@ -6265,7 +8260,7 @@
         <v>-3.4882202136190901E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>8</v>
       </c>
@@ -6285,7 +8280,7 @@
         <v>-3.7796113035970498E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>9</v>
       </c>
@@ -6305,7 +8300,7 @@
         <v>-2.3133702247160599E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>10</v>
       </c>
@@ -6325,7 +8320,7 @@
         <v>-5.5167273454262899E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>11</v>
       </c>
@@ -6345,7 +8340,7 @@
         <v>-5.6387585042915103E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>12</v>
       </c>
@@ -6365,7 +8360,7 @@
         <v>1.5256660666840801E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22">
       <c r="A17">
         <v>13</v>
       </c>
@@ -6385,7 +8380,7 @@
         <v>-6.9065711255477296E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22">
       <c r="A18">
         <v>14</v>
       </c>
@@ -6404,8 +8399,32 @@
       <c r="F18">
         <v>-5.3800626782685703E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="O18">
+        <v>50</v>
+      </c>
+      <c r="P18">
+        <v>40</v>
+      </c>
+      <c r="Q18">
+        <v>4</v>
+      </c>
+      <c r="R18">
+        <v>5</v>
+      </c>
+      <c r="S18">
+        <v>10</v>
+      </c>
+      <c r="T18">
+        <v>12</v>
+      </c>
+      <c r="U18">
+        <v>60</v>
+      </c>
+      <c r="V18">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19">
         <v>15</v>
       </c>
@@ -6424,8 +8443,12 @@
       <c r="F19">
         <v>1.0149237931544001E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="N19">
+        <f>MEDIAN(50,40,4,5,10,12,60,70)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20">
         <v>16</v>
       </c>
@@ -6444,8 +8467,12 @@
       <c r="F20" s="1">
         <v>-6.4077067261997201E-4</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="O20">
+        <f>QUARTILE(O18:U18,3)-QUARTILE(O18:U18,1)</f>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21">
         <v>17</v>
       </c>
@@ -6465,7 +8492,7 @@
         <v>-1.1920192462140201E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22">
       <c r="A22">
         <v>18</v>
       </c>
@@ -6485,7 +8512,7 @@
         <v>-6.97531516784921E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22">
       <c r="A23">
         <v>19</v>
       </c>
@@ -6505,7 +8532,7 @@
         <v>1.5421856974445701E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22">
       <c r="A24">
         <v>20</v>
       </c>
@@ -6525,7 +8552,7 @@
         <v>-3.16746410373868E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22">
       <c r="A25">
         <v>21</v>
       </c>
@@ -6545,7 +8572,7 @@
         <v>-4.3057009789222401E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22">
       <c r="A26">
         <v>22</v>
       </c>
@@ -6565,7 +8592,7 @@
         <v>-4.0151606948934902E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22">
       <c r="A27">
         <v>23</v>
       </c>
@@ -6585,7 +8612,7 @@
         <v>-1.78892856657361E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22">
       <c r="A28">
         <v>24</v>
       </c>
@@ -6605,7 +8632,7 @@
         <v>-6.8941063092096098E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22">
       <c r="A29">
         <v>25</v>
       </c>
@@ -6625,7 +8652,7 @@
         <v>-7.5661382731223503E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22">
       <c r="A30">
         <v>26</v>
       </c>
@@ -6645,7 +8672,7 @@
         <v>-5.39067138134274E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22">
       <c r="A31">
         <v>27</v>
       </c>
@@ -6665,7 +8692,7 @@
         <v>1.8114772385106001E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22">
       <c r="A32">
         <v>28</v>
       </c>
@@ -6685,7 +8712,7 @@
         <v>-1.11879807624626E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>29</v>
       </c>
@@ -6705,7 +8732,7 @@
         <v>1.60627969693857E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -6729,9 +8756,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -6741,7 +8768,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -6755,7 +8782,7 @@
         <v>0.33283355941638099</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -6775,7 +8802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>0</v>
       </c>
@@ -6795,7 +8822,7 @@
         <v>-8.0974129452271405E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6815,7 +8842,7 @@
         <v>1.1177611943135001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -6835,7 +8862,7 @@
         <v>-3.2857375677534601E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
@@ -6855,7 +8882,7 @@
         <v>-2.1183220238527498E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4</v>
       </c>
@@ -6875,7 +8902,7 @@
         <v>-1.8999241952578599E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>5</v>
       </c>
@@ -6895,7 +8922,7 @@
         <v>1.9119309980650801E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>6</v>
       </c>
@@ -6915,7 +8942,7 @@
         <v>-7.0782432186709196E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>7</v>
       </c>
@@ -6935,7 +8962,7 @@
         <v>-2.0304782157437801E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>8</v>
       </c>
@@ -6955,7 +8982,7 @@
         <v>-2.4605847340881601E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>9</v>
       </c>
@@ -6975,7 +9002,7 @@
         <v>-4.0997083396021499E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>10</v>
       </c>
@@ -6995,7 +9022,7 @@
         <v>-2.81743809917434E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>11</v>
       </c>
@@ -7015,7 +9042,7 @@
         <v>-5.5938596089526397E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>12</v>
       </c>
@@ -7035,7 +9062,7 @@
         <v>2.2675628621779899E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>13</v>
       </c>
@@ -7055,7 +9082,7 @@
         <v>-9.0659135082225796E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>14</v>
       </c>
@@ -7075,7 +9102,7 @@
         <v>-4.5720977475325296E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>15</v>
       </c>
@@ -7095,7 +9122,7 @@
         <v>-2.7016668219681499E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>16</v>
       </c>
@@ -7115,7 +9142,7 @@
         <v>-3.2667375157225901E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>17</v>
       </c>
@@ -7135,7 +9162,7 @@
         <v>5.8314486047872297E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>18</v>
       </c>
@@ -7155,7 +9182,7 @@
         <v>-1.7238776689698599E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>19</v>
       </c>
@@ -7175,7 +9202,7 @@
         <v>-9.5777867510127204E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>20</v>
       </c>
@@ -7195,7 +9222,7 @@
         <v>9.0615851833464301E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>21</v>
       </c>
@@ -7215,7 +9242,7 @@
         <v>-5.4431932951686203E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>22</v>
       </c>
@@ -7235,7 +9262,7 @@
         <v>-3.5403511139828702E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>23</v>
       </c>
@@ -7255,7 +9282,7 @@
         <v>-3.6472321048567299E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>24</v>
       </c>
@@ -7275,7 +9302,7 @@
         <v>2.6832081451161299E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>25</v>
       </c>
@@ -7295,7 +9322,7 @@
         <v>-3.5274571843107999E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>26</v>
       </c>
@@ -7315,7 +9342,7 @@
         <v>2.5990513066531602E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>27</v>
       </c>
@@ -7335,7 +9362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>28</v>
       </c>
@@ -7355,7 +9382,7 @@
         <v>5.0382563890175496E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>29</v>
       </c>
@@ -7375,7 +9402,7 @@
         <v>-1.60338391865949E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -7391,7 +9418,7 @@
         <v>0.96701436612971825</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="D39">
         <f>QUARTILE($D$4:$D$33,0)</f>
         <v>-2.7925113231100302E-3</v>
@@ -7405,7 +9432,7 @@
         <v>-7.0782432186709196E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="D40">
         <f>QUARTILE($D$4:$D$33,1)</f>
         <v>3.9509089179294387E-4</v>
@@ -7419,7 +9446,7 @@
         <v>-3.3493909543108125E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="D41">
         <f>QUARTILE($D$4:$D$33,2)</f>
         <v>2.8199461243420499E-3</v>
@@ -7433,7 +9460,7 @@
         <v>-1.7516540569586748E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="D42">
         <f>QUARTILE($D$4:$D$33,3)</f>
         <v>4.2106787343501647E-3</v>
@@ -7447,7 +9474,7 @@
         <v>1.0871214720223323E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="D43">
         <f>QUARTILE($D$4:$D$33,4)</f>
         <v>6.3749054886274503E-3</v>
@@ -7461,7 +9488,7 @@
         <v>5.0382563890175496E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="D45">
         <f>D38-D37</f>
         <v>0</v>
@@ -7471,7 +9498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="D46">
         <f>D39-D38</f>
         <v>-2.7925113231100302E-3</v>
@@ -7481,9 +9508,9 @@
         <v>7.0782432186709196E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="D47">
-        <f t="shared" ref="D47:F50" si="0">D40-D39</f>
+        <f t="shared" ref="D47:D50" si="0">D40-D39</f>
         <v>3.1876022149029742E-3</v>
       </c>
       <c r="F47" s="1">
@@ -7491,7 +9518,7 @@
         <v>-3.7288522643601071E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="D48">
         <f t="shared" si="0"/>
         <v>2.4248552325491059E-3</v>
@@ -7501,7 +9528,7 @@
         <v>-1.5977368973521377E-3</v>
       </c>
     </row>
-    <row r="49" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:6">
       <c r="D49">
         <f t="shared" si="0"/>
         <v>1.3907326100081148E-3</v>
@@ -7511,7 +9538,7 @@
         <v>-1.860366204160908E-3</v>
       </c>
     </row>
-    <row r="50" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:6">
       <c r="D50">
         <f t="shared" si="0"/>
         <v>2.1642267542772856E-3</v>
@@ -7528,9 +9555,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -7540,7 +9567,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -7554,7 +9581,7 @@
         <v>0.51719187154758695</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -7574,7 +9601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>0</v>
       </c>
@@ -7594,7 +9621,7 @@
         <v>-1.2119754075568499E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
@@ -7614,7 +9641,7 @@
         <v>-5.9026780993743999E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -7634,7 +9661,7 @@
         <v>1.31836055900639E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
@@ -7654,7 +9681,7 @@
         <v>-1.67674038697403E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4</v>
       </c>
@@ -7674,7 +9701,7 @@
         <v>-1.0142672573018E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>5</v>
       </c>
@@ -7694,7 +9721,7 @@
         <v>-1.2517411531936799E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>6</v>
       </c>
@@ -7714,7 +9741,7 @@
         <v>1.9154975424234199E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>7</v>
       </c>
@@ -7734,7 +9761,7 @@
         <v>-6.99970418727946E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>8</v>
       </c>
@@ -7754,7 +9781,7 @@
         <v>-3.2579873770000002E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>9</v>
       </c>
@@ -7774,7 +9801,7 @@
         <v>-2.6419898658634998E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>10</v>
       </c>
@@ -7794,7 +9821,7 @@
         <v>-1.3954769173487499E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>11</v>
       </c>
@@ -7814,7 +9841,7 @@
         <v>-4.8550550644500803E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>12</v>
       </c>
@@ -7834,7 +9861,7 @@
         <v>-5.0990232070927399E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>13</v>
       </c>
@@ -7854,7 +9881,7 @@
         <v>-1.7819612863766499E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>14</v>
       </c>
@@ -7874,7 +9901,7 @@
         <v>-1.1371158191845501E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>15</v>
       </c>
@@ -7894,7 +9921,7 @@
         <v>3.9224771035693801E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>16</v>
       </c>
@@ -7914,7 +9941,7 @@
         <v>-1.3571533176202999E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>17</v>
       </c>
@@ -7934,7 +9961,7 @@
         <v>-2.6017640606640298E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>18</v>
       </c>
@@ -7954,7 +9981,7 @@
         <v>-5.7224645484128204E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>19</v>
       </c>
@@ -7974,7 +10001,7 @@
         <v>-8.8889988539172793E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>20</v>
       </c>
@@ -7994,7 +10021,7 @@
         <v>-5.8806215826587198E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>21</v>
       </c>
@@ -8014,7 +10041,7 @@
         <v>-2.59241435319469E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>22</v>
       </c>
@@ -8034,7 +10061,7 @@
         <v>-6.6292179250593501E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>23</v>
       </c>
@@ -8054,7 +10081,7 @@
         <v>-1.0078287593559099E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>24</v>
       </c>
@@ -8074,7 +10101,7 @@
         <v>-6.3987936206359999E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>25</v>
       </c>
@@ -8094,7 +10121,7 @@
         <v>-8.1884611163008502E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>26</v>
       </c>
@@ -8114,7 +10141,7 @@
         <v>-8.6311564224213905E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>27</v>
       </c>
@@ -8134,7 +10161,7 @@
         <v>-8.2549595578293705E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>28</v>
       </c>
@@ -8154,7 +10181,7 @@
         <v>-1.08959930176485E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>29</v>
       </c>
@@ -8174,7 +10201,7 @@
         <v>-7.0021476630840996E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -8190,7 +10217,7 @@
         <v>0.98451978129199669</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="D39">
         <f>QUARTILE($D$4:$D$33,0)</f>
         <v>-5.6410577857612899E-4</v>
@@ -8200,7 +10227,7 @@
         <v>-1.3954769173487499E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="D40">
         <f>QUARTILE($D$4:$D$33,1)</f>
         <v>2.1502800157512875E-3</v>
@@ -8210,7 +10237,7 @@
         <v>-7.8912718840455018E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="D41">
         <f>QUARTILE($D$4:$D$33,2)</f>
         <v>4.4350223274996449E-3</v>
@@ -8220,7 +10247,7 @@
         <v>-4.9770391357714105E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="D42">
         <f>QUARTILE($D$4:$D$33,3)</f>
         <v>6.0704804641376602E-3</v>
@@ -8230,7 +10257,7 @@
         <v>-1.1201933282128499E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="D43">
         <f>QUARTILE($D$4:$D$33,4)</f>
         <v>1.06046338090119E-2</v>
@@ -8240,7 +10267,7 @@
         <v>1.9154975424234199E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="D45">
         <f>D38-D37</f>
         <v>0</v>
@@ -8250,7 +10277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="D46">
         <f>D39-D38</f>
         <v>-5.6410577857612899E-4</v>
@@ -8260,7 +10287,7 @@
         <v>-1.3954769173487499E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="D47">
         <f t="shared" ref="D47:F50" si="0">D40-D39</f>
         <v>2.7143857943274165E-3</v>
@@ -8270,7 +10297,7 @@
         <v>6.0634972894419974E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="D48">
         <f t="shared" si="0"/>
         <v>2.2847423117483574E-3</v>
@@ -8280,7 +10307,7 @@
         <v>2.9142327482740912E-3</v>
       </c>
     </row>
-    <row r="49" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:6">
       <c r="D49">
         <f t="shared" si="0"/>
         <v>1.6354581366380154E-3</v>
@@ -8290,7 +10317,7 @@
         <v>3.8568458075585606E-3</v>
       </c>
     </row>
-    <row r="50" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:6">
       <c r="D50">
         <f t="shared" si="0"/>
         <v>4.5341533448742394E-3</v>
@@ -8307,9 +10334,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -8319,7 +10346,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -8333,7 +10360,7 @@
         <v>0.66617361728492197</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -8353,7 +10380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>0</v>
       </c>
@@ -8373,7 +10400,7 @@
         <v>4.0554145517913099E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8393,7 +10420,7 @@
         <v>0.279595935073226</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -8413,7 +10440,7 @@
         <v>-1.8706740924329099E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
@@ -8433,7 +10460,7 @@
         <v>-3.2570612161153501E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4</v>
       </c>
@@ -8453,7 +10480,7 @@
         <v>-0.25458930937267898</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>5</v>
       </c>
@@ -8473,7 +10500,7 @@
         <v>-0.21675477052320299</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>6</v>
       </c>
@@ -8493,7 +10520,7 @@
         <v>2.91664938337582E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>7</v>
       </c>
@@ -8513,7 +10540,7 @@
         <v>0.104297651062652</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>8</v>
       </c>
@@ -8533,7 +10560,7 @@
         <v>4.3715158959601796E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>9</v>
       </c>
@@ -8553,7 +10580,7 @@
         <v>-3.91949096680555E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>10</v>
       </c>
@@ -8573,7 +10600,7 @@
         <v>1.91910487543472E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>11</v>
       </c>
@@ -8593,7 +10620,7 @@
         <v>-6.0679295346903099E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>12</v>
       </c>
@@ -8613,7 +10640,7 @@
         <v>3.9748435611588204E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>13</v>
       </c>
@@ -8633,7 +10660,7 @@
         <v>5.7916706645013598E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>14</v>
       </c>
@@ -8653,7 +10680,7 @@
         <v>4.2894481460590802E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>15</v>
       </c>
@@ -8673,7 +10700,7 @@
         <v>7.8711482512001205E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>16</v>
       </c>
@@ -8693,7 +10720,7 @@
         <v>1.4486254408815299E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>17</v>
       </c>
@@ -8713,7 +10740,7 @@
         <v>9.8627864801995702E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>18</v>
       </c>
@@ -8733,7 +10760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>19</v>
       </c>
@@ -8753,7 +10780,7 @@
         <v>-9.7910468117792998E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>20</v>
       </c>
@@ -8773,7 +10800,7 @@
         <v>4.7719312585747797E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>21</v>
       </c>
@@ -8793,7 +10820,7 @@
         <v>2.1047689339612698E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>22</v>
       </c>
@@ -8813,7 +10840,7 @@
         <v>-5.5136005584197002E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>23</v>
       </c>
@@ -8833,7 +10860,7 @@
         <v>-7.6083237656365799E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>24</v>
       </c>
@@ -8853,7 +10880,7 @@
         <v>5.2323261747570697E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>25</v>
       </c>
@@ -8873,7 +10900,7 @@
         <v>0.131960652140344</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>26</v>
       </c>
@@ -8893,7 +10920,7 @@
         <v>5.1836604315231599E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>27</v>
       </c>
@@ -8913,7 +10940,7 @@
         <v>-1.80039045323332E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>28</v>
       </c>
@@ -8933,7 +10960,7 @@
         <v>6.6104754297627803E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>29</v>
       </c>
@@ -8953,7 +10980,7 @@
         <v>0.27240253349211102</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -8976,9 +11003,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -8988,7 +11015,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -9002,7 +11029,7 @@
         <v>0.40590724234006298</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -9022,7 +11049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>0</v>
       </c>
@@ -9042,7 +11069,7 @@
         <v>3.8198108154760902E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
@@ -9062,7 +11089,7 @@
         <v>-1.2142214752381799</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -9082,7 +11109,7 @@
         <v>-7.0074214958807002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
@@ -9102,7 +11129,7 @@
         <v>9.3640710508028097E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4</v>
       </c>
@@ -9122,7 +11149,7 @@
         <v>-1.1840350230275001</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>5</v>
       </c>
@@ -9142,7 +11169,7 @@
         <v>-0.34271872271019399</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>6</v>
       </c>
@@ -9162,7 +11189,7 @@
         <v>1.54688456743761E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>7</v>
       </c>
@@ -9182,7 +11209,7 @@
         <v>-2.01434853155701E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>8</v>
       </c>
@@ -9202,7 +11229,7 @@
         <v>1.4505734973628399E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>9</v>
       </c>
@@ -9222,7 +11249,7 @@
         <v>8.9788680184770594E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>10</v>
       </c>
@@ -9242,7 +11269,7 @@
         <v>1.5916220751723699E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>11</v>
       </c>
@@ -9262,7 +11289,7 @@
         <v>-0.31100727658218902</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>12</v>
       </c>
@@ -9282,7 +11309,7 @@
         <v>-5.0674695337909699E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>13</v>
       </c>
@@ -9302,7 +11329,7 @@
         <v>-8.5323927216879494E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>14</v>
       </c>
@@ -9322,7 +11349,7 @@
         <v>1.5645896908951299E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>15</v>
       </c>
@@ -9342,7 +11369,7 @@
         <v>-2.3754180001397399E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>16</v>
       </c>
@@ -9362,7 +11389,7 @@
         <v>-1.06692643429668</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>17</v>
       </c>
@@ -9382,7 +11409,7 @@
         <v>1.6243311531219599E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>18</v>
       </c>
@@ -9402,7 +11429,7 @@
         <v>-0.46301180079864301</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>19</v>
       </c>
@@ -9422,7 +11449,7 @@
         <v>-1.69854676244289</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>20</v>
       </c>
@@ -9442,7 +11469,7 @@
         <v>-0.94912546798061004</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>21</v>
       </c>
@@ -9462,7 +11489,7 @@
         <v>-1.80430025814446</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>22</v>
       </c>
@@ -9482,7 +11509,7 @@
         <v>1.33636024190034E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>23</v>
       </c>
@@ -9502,7 +11529,7 @@
         <v>-0.25131193831996201</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>24</v>
       </c>
@@ -9522,7 +11549,7 @@
         <v>-0.48756962261563502</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>25</v>
       </c>
@@ -9542,7 +11569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>26</v>
       </c>
@@ -9562,7 +11589,7 @@
         <v>-2.6095160997089502E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>27</v>
       </c>
@@ -9582,7 +11609,7 @@
         <v>-0.74697105233851402</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>28</v>
       </c>
@@ -9602,7 +11629,7 @@
         <v>1.8625747914139301E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>29</v>
       </c>
@@ -9622,7 +11649,7 @@
         <v>-0.38463177904765999</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -9638,7 +11665,7 @@
         <v>0.57649171111802644</v>
       </c>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:6">
       <c r="F55" s="1"/>
     </row>
   </sheetData>
@@ -9653,9 +11680,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -9665,7 +11692,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -9679,7 +11706,7 @@
         <v>0.46783583650461702</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -9699,7 +11726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>0</v>
       </c>
@@ -9719,7 +11746,7 @@
         <v>-3.6535029671500102E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
@@ -9739,7 +11766,7 @@
         <v>1.4675506133468E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -9759,7 +11786,7 @@
         <v>-2.3010561786476701E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
@@ -9779,7 +11806,7 @@
         <v>-2.9082730606477199E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4</v>
       </c>
@@ -9799,7 +11826,7 @@
         <v>3.3547020427374799E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>5</v>
       </c>
@@ -9819,7 +11846,7 @@
         <v>-2.7226830001258098E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>6</v>
       </c>
@@ -9839,7 +11866,7 @@
         <v>1.47153077308439E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>7</v>
       </c>
@@ -9859,7 +11886,7 @@
         <v>2.6752615165469101E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>8</v>
       </c>
@@ -9879,7 +11906,7 @@
         <v>4.3015006239444598E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>9</v>
       </c>
@@ -9899,7 +11926,7 @@
         <v>-1.2398493184265801E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>10</v>
       </c>
@@ -9919,7 +11946,7 @@
         <v>-1.1238123454104E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>11</v>
       </c>
@@ -9939,7 +11966,7 @@
         <v>-6.4259516686617701E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>12</v>
       </c>
@@ -9959,7 +11986,7 @@
         <v>-1.5040684506399201E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>13</v>
       </c>
@@ -9979,7 +12006,7 @@
         <v>1.1710418563115599E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>14</v>
       </c>
@@ -9999,7 +12026,7 @@
         <v>-1.8614187586653699E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>15</v>
       </c>
@@ -10019,7 +12046,7 @@
         <v>-2.11779337502087E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>16</v>
       </c>
@@ -10039,7 +12066,7 @@
         <v>2.9152638894912502E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>17</v>
       </c>
@@ -10059,7 +12086,7 @@
         <v>9.1143764287142798E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>18</v>
       </c>
@@ -10079,7 +12106,7 @@
         <v>2.9163089003310799E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>19</v>
       </c>
@@ -10099,7 +12126,7 @@
         <v>-7.3466645591996305E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>20</v>
       </c>
@@ -10119,7 +12146,7 @@
         <v>-1.4474323063490099E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>21</v>
       </c>
@@ -10139,7 +12166,7 @@
         <v>-1.4666085283480399E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>22</v>
       </c>
@@ -10159,7 +12186,7 @@
         <v>5.4873279348653901E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>23</v>
       </c>
@@ -10179,7 +12206,7 @@
         <v>3.3292849450299498E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>24</v>
       </c>
@@ -10199,7 +12226,7 @@
         <v>1.8729859539121201E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>25</v>
       </c>
@@ -10219,7 +12246,7 @@
         <v>2.3295079612731802E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>26</v>
       </c>
@@ -10239,7 +12266,7 @@
         <v>-8.20997221326214E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>27</v>
       </c>
@@ -10259,7 +12286,7 @@
         <v>7.7431777921155298E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>28</v>
       </c>
@@ -10279,7 +12306,7 @@
         <v>3.8305146468709902E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>29</v>
       </c>
@@ -10299,7 +12326,7 @@
         <v>-1.21740165450427E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -10319,4 +12346,1271 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1">
+        <v>200</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1">
+        <v>9.5583254269994297E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>305</v>
+      </c>
+      <c r="C4">
+        <v>-10500</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-3.1801546553360201E-4</v>
+      </c>
+      <c r="E4">
+        <v>0.97370024211095996</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2.27901221423021E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>125</v>
+      </c>
+      <c r="C5">
+        <v>7500</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.64620305936682E-4</v>
+      </c>
+      <c r="E5">
+        <v>0.96764513046827105</v>
+      </c>
+      <c r="F5">
+        <v>2.31108570802218E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>166</v>
+      </c>
+      <c r="C6">
+        <v>3400</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.9153461129646401E-4</v>
+      </c>
+      <c r="E6">
+        <v>0.96970234590405902</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2.55072751944751E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>72</v>
+      </c>
+      <c r="C7">
+        <v>12800</v>
+      </c>
+      <c r="D7" s="1">
+        <v>9.8510600016654595E-4</v>
+      </c>
+      <c r="E7">
+        <v>0.96074775966049197</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1.33229755167912E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>112</v>
+      </c>
+      <c r="C8">
+        <v>8800</v>
+      </c>
+      <c r="D8" s="1">
+        <v>9.7490486909723696E-4</v>
+      </c>
+      <c r="E8">
+        <v>0.96180051367393204</v>
+      </c>
+      <c r="F8">
+        <v>-2.8956791023078102E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>184</v>
+      </c>
+      <c r="C9">
+        <v>1600</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-5.7204533290029704E-4</v>
+      </c>
+      <c r="E9">
+        <v>0.96908779280389701</v>
+      </c>
+      <c r="F9">
+        <v>1.55060996987099E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>447</v>
+      </c>
+      <c r="C10">
+        <v>-24700</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-3.4586315030063399E-4</v>
+      </c>
+      <c r="E10">
+        <v>0.97282447417940499</v>
+      </c>
+      <c r="F10">
+        <v>1.3370711879616599E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>67</v>
+      </c>
+      <c r="C11">
+        <v>13300</v>
+      </c>
+      <c r="D11">
+        <v>1.36159989936833E-3</v>
+      </c>
+      <c r="E11">
+        <v>0.95591789197715604</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-2.64351000704543E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>60</v>
+      </c>
+      <c r="C12">
+        <v>14000</v>
+      </c>
+      <c r="D12">
+        <v>2.61089606841617E-3</v>
+      </c>
+      <c r="E12">
+        <v>0.93934772836331304</v>
+      </c>
+      <c r="F12">
+        <v>-1.7008091382262299E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>217</v>
+      </c>
+      <c r="C13">
+        <v>-1700</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7.1080800553879799E-4</v>
+      </c>
+      <c r="E13">
+        <v>0.96743453215519704</v>
+      </c>
+      <c r="F13">
+        <v>-4.7348999076028903E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>125</v>
+      </c>
+      <c r="C14">
+        <v>7500</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4.8884289373757296E-4</v>
+      </c>
+      <c r="E14">
+        <v>0.96697077236213902</v>
+      </c>
+      <c r="F14" s="1">
+        <v>-1.9583094439135001E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>186</v>
+      </c>
+      <c r="C15">
+        <v>1400</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1.3607610937584001E-4</v>
+      </c>
+      <c r="E15">
+        <v>0.96938022907993104</v>
+      </c>
+      <c r="F15">
+        <v>-1.01979899980586E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16">
+        <v>500</v>
+      </c>
+      <c r="C16">
+        <v>-30000</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2.01202052447987E-4</v>
+      </c>
+      <c r="E16">
+        <v>0.97100148527699903</v>
+      </c>
+      <c r="F16" s="1">
+        <v>-1.6976618436987301E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17">
+        <v>115</v>
+      </c>
+      <c r="C17">
+        <v>8500</v>
+      </c>
+      <c r="D17" s="1">
+        <v>-2.3307219212684299E-4</v>
+      </c>
+      <c r="E17">
+        <v>0.96800242773667999</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1.3509037897166899E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18">
+        <v>61</v>
+      </c>
+      <c r="C18">
+        <v>13900</v>
+      </c>
+      <c r="D18">
+        <v>3.6741715523751399E-3</v>
+      </c>
+      <c r="E18">
+        <v>0.93361738083558998</v>
+      </c>
+      <c r="F18">
+        <v>-4.0251692337766598E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <v>132</v>
+      </c>
+      <c r="C19">
+        <v>6800</v>
+      </c>
+      <c r="D19" s="1">
+        <v>9.3690642965105195E-5</v>
+      </c>
+      <c r="E19">
+        <v>0.96926544854748797</v>
+      </c>
+      <c r="F19">
+        <v>-3.9144852080597002E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>164</v>
+      </c>
+      <c r="C20">
+        <v>3600</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2.44456738139609E-5</v>
+      </c>
+      <c r="E20">
+        <v>0.970489023828774</v>
+      </c>
+      <c r="F20">
+        <v>-1.2018872661650401E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21">
+        <v>64</v>
+      </c>
+      <c r="C21">
+        <v>13600</v>
+      </c>
+      <c r="D21">
+        <v>1.48931757631518E-3</v>
+      </c>
+      <c r="E21">
+        <v>0.95709806533036701</v>
+      </c>
+      <c r="F21" s="1">
+        <v>6.9685420040077595E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22">
+        <v>225</v>
+      </c>
+      <c r="C22">
+        <v>-2500</v>
+      </c>
+      <c r="D22" s="1">
+        <v>-3.0376040242210901E-4</v>
+      </c>
+      <c r="E22">
+        <v>0.97102582323233899</v>
+      </c>
+      <c r="F22" s="1">
+        <v>8.8558447095388095E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23">
+        <v>111</v>
+      </c>
+      <c r="C23">
+        <v>8900</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3.11250009935037E-6</v>
+      </c>
+      <c r="E23">
+        <v>0.96581088631690404</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3.3914477067993301E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24">
+        <v>86</v>
+      </c>
+      <c r="C24">
+        <v>11400</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9.2771310818171005E-4</v>
+      </c>
+      <c r="E24">
+        <v>0.96107430764671098</v>
+      </c>
+      <c r="F24" s="1">
+        <v>-3.6699534450201901E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="B25">
+        <v>223</v>
+      </c>
+      <c r="C25">
+        <v>-2300</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-1.9873699663539E-5</v>
+      </c>
+      <c r="E25">
+        <v>0.97193370567787496</v>
+      </c>
+      <c r="F25">
+        <v>1.6901728547010701E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26">
+        <v>115</v>
+      </c>
+      <c r="C26">
+        <v>8500</v>
+      </c>
+      <c r="D26" s="1">
+        <v>-3.9489483888307998E-5</v>
+      </c>
+      <c r="E26">
+        <v>0.96976658251598502</v>
+      </c>
+      <c r="F26">
+        <v>3.5566008574485701E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="B27">
+        <v>117</v>
+      </c>
+      <c r="C27">
+        <v>8300</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3.2300768838633399E-4</v>
+      </c>
+      <c r="E27">
+        <v>0.96822540749888197</v>
+      </c>
+      <c r="F27">
+        <v>2.34240809806618E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28">
+        <v>103</v>
+      </c>
+      <c r="C28">
+        <v>9700</v>
+      </c>
+      <c r="D28" s="1">
+        <v>4.1058889236392199E-4</v>
+      </c>
+      <c r="E28">
+        <v>0.96215382934632898</v>
+      </c>
+      <c r="F28">
+        <v>-3.8331853111473698E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29">
+        <v>58</v>
+      </c>
+      <c r="C29">
+        <v>14200</v>
+      </c>
+      <c r="D29">
+        <v>1.83884645697647E-3</v>
+      </c>
+      <c r="E29">
+        <v>0.94826194358431004</v>
+      </c>
+      <c r="F29">
+        <v>-4.2334451023048301E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="B30">
+        <v>293</v>
+      </c>
+      <c r="C30">
+        <v>-9300</v>
+      </c>
+      <c r="D30" s="1">
+        <v>4.6998691859048702E-4</v>
+      </c>
+      <c r="E30">
+        <v>0.96876352850951697</v>
+      </c>
+      <c r="F30">
+        <v>1.35265354365587E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>27</v>
+      </c>
+      <c r="B31">
+        <v>173</v>
+      </c>
+      <c r="C31">
+        <v>2700</v>
+      </c>
+      <c r="D31" s="1">
+        <v>4.4630750775029299E-4</v>
+      </c>
+      <c r="E31">
+        <v>0.96711761286522102</v>
+      </c>
+      <c r="F31" s="1">
+        <v>-2.94054514192437E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>28</v>
+      </c>
+      <c r="B32">
+        <v>170</v>
+      </c>
+      <c r="C32">
+        <v>3000</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1.56662067031118E-4</v>
+      </c>
+      <c r="E32">
+        <v>0.97023098286588105</v>
+      </c>
+      <c r="F32">
+        <v>-6.8809596209191597E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>29</v>
+      </c>
+      <c r="B33">
+        <v>179</v>
+      </c>
+      <c r="C33">
+        <v>2100</v>
+      </c>
+      <c r="D33" s="1">
+        <v>-1.2096758338177301E-4</v>
+      </c>
+      <c r="E33">
+        <v>0.97039641936019505</v>
+      </c>
+      <c r="F33" s="1">
+        <v>-5.1583751087591601E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34">
+        <f>SUM(C4:C33)</f>
+        <v>104500</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34">
+        <f>AVERAGE(E4:E33)</f>
+        <v>0.9646264757904931</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:I27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:9">
+      <c r="B2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="13">
+        <f>AVERAGE(ZDT1!C4:C33)</f>
+        <v>5493.333333333333</v>
+      </c>
+      <c r="E4" s="13">
+        <f>STDEV(ZDT1!C4:C33)</f>
+        <v>2464.357415486716</v>
+      </c>
+      <c r="F4" s="13">
+        <f>AVERAGE([2]ZDT1!C4:C33)</f>
+        <v>-5593.333333333333</v>
+      </c>
+      <c r="G4" s="13">
+        <f>STDEV([2]ZDT1!C4:C33)</f>
+        <v>7159.1722375171821</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" s="16"/>
+      <c r="C5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5">
+        <f>AVERAGE(ZDT1!D4:D33)</f>
+        <v>5.8712459443867222E-3</v>
+      </c>
+      <c r="E5" s="5">
+        <f>STDEV(ZDT1!D4:D33)</f>
+        <v>3.5729970109722774E-3</v>
+      </c>
+      <c r="F5" s="5">
+        <f>AVERAGE([2]ZDT1!D4:D33)</f>
+        <v>-1.4504204644586664E-3</v>
+      </c>
+      <c r="G5" s="5">
+        <f>STDEV([2]ZDT1!D4:D33)</f>
+        <v>2.682409302175151E-3</v>
+      </c>
+      <c r="I5" s="1">
+        <f>MIN(D5,D9,D13,D17,D25,D21)</f>
+        <v>5.2434513633378645E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="16"/>
+      <c r="C6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <f>AVERAGE(ZDT1!F4:F33)</f>
+        <v>-2.9706086445590754E-3</v>
+      </c>
+      <c r="E6" s="5">
+        <f>STDEV(ZDT1!F4:F33)</f>
+        <v>3.431297630386763E-3</v>
+      </c>
+      <c r="F6" s="5">
+        <f>AVERAGE([2]ZDT1!F4:F33)</f>
+        <v>9.6789247509792729E-4</v>
+      </c>
+      <c r="G6" s="5">
+        <f>STDEV([2]ZDT1!F4:F33)</f>
+        <v>2.3162808710606637E-3</v>
+      </c>
+      <c r="I6" s="1">
+        <f>MAX(D5,D9,D13,D17,D25,D21)</f>
+        <v>8.797703848114102E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="17"/>
+      <c r="C7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="11">
+        <f>AVERAGE(ZDT1!E4:E33)</f>
+        <v>0.97931063445484523</v>
+      </c>
+      <c r="E7" s="11">
+        <f>STDEV(ZDT1!E4:E33)</f>
+        <v>5.5035818437325938E-3</v>
+      </c>
+      <c r="F7" s="11">
+        <f>AVERAGE([2]ZDT1!E4:E33)</f>
+        <v>0.98920589449306362</v>
+      </c>
+      <c r="G7" s="11">
+        <f>STDEV([2]ZDT1!E4:E33)</f>
+        <v>3.6099371088204111E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="13">
+        <f>AVERAGE(ZDT2!C4:C33)</f>
+        <v>2260</v>
+      </c>
+      <c r="E8" s="13">
+        <f>STDEV(ZDT2!C4:C33)</f>
+        <v>3114.1058383448999</v>
+      </c>
+      <c r="F8" s="13">
+        <f>AVERAGE([2]ZDT2!C4:C33)</f>
+        <v>-12710</v>
+      </c>
+      <c r="G8" s="13">
+        <f>STDEV([2]ZDT2!C4:C33)</f>
+        <v>11295.447664038575</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="16"/>
+      <c r="C9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="5">
+        <f>AVERAGE(ZDT2!D4:D33)</f>
+        <v>2.4462588688873299E-3</v>
+      </c>
+      <c r="E9" s="5">
+        <f>STDEV(ZDT2!D4:D33)</f>
+        <v>2.4192892362519861E-3</v>
+      </c>
+      <c r="F9" s="5">
+        <f>AVERAGE([2]ZDT2!D4:D33)</f>
+        <v>-7.7226032443536968E-3</v>
+      </c>
+      <c r="G9" s="5">
+        <f>STDEV([2]ZDT2!D4:D33)</f>
+        <v>1.4868639033140696E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="16"/>
+      <c r="C10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="5">
+        <f>AVERAGE(ZDT2!F4:F33)</f>
+        <v>-1.5038368534341089E-3</v>
+      </c>
+      <c r="E10" s="5">
+        <f>STDEV(ZDT2!F4:F33)</f>
+        <v>2.6931888704388725E-3</v>
+      </c>
+      <c r="F10" s="5">
+        <f>AVERAGE([2]ZDT2!F4:F33)</f>
+        <v>4.1422618540345311E-2</v>
+      </c>
+      <c r="G10" s="5">
+        <f>STDEV([2]ZDT2!F4:F33)</f>
+        <v>0.12172660266913846</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="17"/>
+      <c r="C11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="11">
+        <f>AVERAGE(ZDT2!E4:E33)</f>
+        <v>0.96701436612971825</v>
+      </c>
+      <c r="E11" s="11">
+        <f>STDEV(ZDT2!E4:E33)</f>
+        <v>7.1863908481972589E-3</v>
+      </c>
+      <c r="F11" s="11">
+        <f>AVERAGE([2]ZDT2!E4:E33)</f>
+        <v>0.98119115751499442</v>
+      </c>
+      <c r="G11" s="11">
+        <f>STDEV([2]ZDT2!E4:E33)</f>
+        <v>5.7688357787110244E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="13">
+        <f>AVERAGE(ZDT3!C4:C33)</f>
+        <v>5030</v>
+      </c>
+      <c r="E12" s="13">
+        <f>STDEV(ZDT3!C4:C33)</f>
+        <v>2538.822697561839</v>
+      </c>
+      <c r="F12" s="13">
+        <f>AVERAGE([2]ZDT3!C4:C33)</f>
+        <v>-3706.6666666666665</v>
+      </c>
+      <c r="G12" s="13">
+        <f>STDEV([2]ZDT3!C4:C33)</f>
+        <v>9862.3957827047598</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="16"/>
+      <c r="C13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5">
+        <f>AVERAGE(ZDT3!D4:D33)</f>
+        <v>4.3371984293000786E-3</v>
+      </c>
+      <c r="E13" s="5">
+        <f>STDEV(ZDT3!D4:D33)</f>
+        <v>2.9078851868012895E-3</v>
+      </c>
+      <c r="F13" s="5">
+        <f>AVERAGE([2]ZDT3!D4:D33)</f>
+        <v>2.2912545419477093E-3</v>
+      </c>
+      <c r="G13" s="5">
+        <f>STDEV([2]ZDT3!D4:D33)</f>
+        <v>1.4358361485530238E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="16"/>
+      <c r="C14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="5">
+        <f>AVERAGE(ZDT3!F4:F33)</f>
+        <v>-4.7253103495579684E-3</v>
+      </c>
+      <c r="E14" s="5">
+        <f>STDEV(ZDT3!F4:F33)</f>
+        <v>4.3402967291538965E-3</v>
+      </c>
+      <c r="F14" s="5">
+        <f>AVERAGE([2]ZDT3!F4:F33)</f>
+        <v>-4.3432941611295161E-3</v>
+      </c>
+      <c r="G14" s="5">
+        <f>STDEV([2]ZDT3!F4:F33)</f>
+        <v>2.4086556702087061E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="17"/>
+      <c r="C15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="11">
+        <f>AVERAGE(ZDT3!E4:E33)</f>
+        <v>0.98451978129199669</v>
+      </c>
+      <c r="E15" s="11">
+        <f>STDEV(ZDT3!E4:E33)</f>
+        <v>5.7225179038717837E-3</v>
+      </c>
+      <c r="F15" s="11">
+        <f>AVERAGE([2]ZDT3!E4:E33)</f>
+        <v>0.98531081408259802</v>
+      </c>
+      <c r="G15" s="11">
+        <f>STDEV([2]ZDT3!E4:E33)</f>
+        <v>2.7756297086266094E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="13">
+        <f>AVERAGE(ZDT4!C4:C33)</f>
+        <v>-3970</v>
+      </c>
+      <c r="E16" s="13">
+        <f>STDEV(ZDT4!C4:C33)</f>
+        <v>5839.2341255008605</v>
+      </c>
+      <c r="F16" s="13">
+        <f>AVERAGE([2]ZDT4!C4:C33)</f>
+        <v>-17803.333333333332</v>
+      </c>
+      <c r="G16" s="13">
+        <f>STDEV([2]ZDT4!C4:C33)</f>
+        <v>11662.834674455355</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="16"/>
+      <c r="C17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5">
+        <f>AVERAGE(ZDT4!D4:D33)</f>
+        <v>8.797703848114102E-3</v>
+      </c>
+      <c r="E17" s="5">
+        <f>STDEV(ZDT4!D4:D33)</f>
+        <v>8.050179774649735E-2</v>
+      </c>
+      <c r="F17" s="5">
+        <f>AVERAGE([2]ZDT4!D4:D33)</f>
+        <v>4.8260873025495997E-3</v>
+      </c>
+      <c r="G17" s="5">
+        <f>STDEV([2]ZDT4!D4:D33)</f>
+        <v>0.14256837030049149</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="16"/>
+      <c r="C18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="5">
+        <f>AVERAGE(ZDT4!F4:F33)</f>
+        <v>1.5767553284374937E-2</v>
+      </c>
+      <c r="E18" s="5">
+        <f>STDEV(ZDT4!F4:F33)</f>
+        <v>0.10436017372467146</v>
+      </c>
+      <c r="F18" s="5">
+        <f>AVERAGE([2]ZDT4!F4:F33)</f>
+        <v>6.1105781271712324E-2</v>
+      </c>
+      <c r="G18" s="5">
+        <f>STDEV([2]ZDT4!F4:F33)</f>
+        <v>0.30035859770009959</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="17"/>
+      <c r="C19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="11">
+        <f>AVERAGE(ZDT4!E4:E33)</f>
+        <v>0.94645006033241097</v>
+      </c>
+      <c r="E19" s="11">
+        <f>STDEV(ZDT4!E4:E33)</f>
+        <v>0.10261301438429161</v>
+      </c>
+      <c r="F19" s="11">
+        <f>AVERAGE([2]ZDT4!E4:E33)</f>
+        <v>0.92737742718484084</v>
+      </c>
+      <c r="G19" s="11">
+        <f>STDEV([2]ZDT4!E4:E33)</f>
+        <v>0.19898209936606981</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="13">
+        <f>AVERAGE(DTLZ2!C4:C33)</f>
+        <v>19106.666666666668</v>
+      </c>
+      <c r="E20" s="13">
+        <f>STDEV(DTLZ2!C4:C33)</f>
+        <v>2159.6508870701687</v>
+      </c>
+      <c r="F20" s="13">
+        <f>AVERAGE([2]DTLZ2!C4:C33)</f>
+        <v>15173.333333333334</v>
+      </c>
+      <c r="G20" s="13">
+        <f>STDEV([2]DTLZ2!C4:C33)</f>
+        <v>6152.0915049320811</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="16"/>
+      <c r="C21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="5">
+        <f>AVERAGE(DTLZ2!D4:D33)</f>
+        <v>2.8170767396039353E-3</v>
+      </c>
+      <c r="E21" s="5">
+        <f>STDEV(DTLZ2!D4:D33)</f>
+        <v>7.8476437382925916E-3</v>
+      </c>
+      <c r="F21" s="5">
+        <f>AVERAGE([2]DTLZ2!D4:D33)</f>
+        <v>3.846387424315765E-3</v>
+      </c>
+      <c r="G21" s="5">
+        <f>STDEV([2]DTLZ2!D4:D33)</f>
+        <v>4.8120945537095663E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="16"/>
+      <c r="C22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="5">
+        <f>AVERAGE(DTLZ2!F4:F33)</f>
+        <v>3.9826148063249588E-3</v>
+      </c>
+      <c r="E22" s="5">
+        <f>STDEV(DTLZ2!F4:F33)</f>
+        <v>2.6609746389542669E-2</v>
+      </c>
+      <c r="F22" s="5">
+        <f>AVERAGE([2]DTLZ2!F4:F33)</f>
+        <v>-2.4490873861368482E-3</v>
+      </c>
+      <c r="G22" s="5">
+        <f>STDEV([2]DTLZ2!F4:F33)</f>
+        <v>1.1788804032500315E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="17"/>
+      <c r="C23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="11">
+        <f>AVERAGE(DTLZ2!E4:E33)</f>
+        <v>0.79160620050158537</v>
+      </c>
+      <c r="E23" s="11">
+        <f>STDEV(DTLZ2!E4:E33)</f>
+        <v>1.3596699611337693E-2</v>
+      </c>
+      <c r="F23" s="11">
+        <f>AVERAGE([2]DTLZ2!E4:E33)</f>
+        <v>0.85751866938468002</v>
+      </c>
+      <c r="G23" s="11">
+        <f>STDEV([2]DTLZ2!E4:E33)</f>
+        <v>8.9307924910633947E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="13">
+        <f>AVERAGE(DTLZ5!C4:C33)</f>
+        <v>3483.3333333333335</v>
+      </c>
+      <c r="E24" s="13">
+        <f>STDEV(DTLZ5!C4:C33)</f>
+        <v>10629.110428711667</v>
+      </c>
+      <c r="F24" s="13">
+        <f>AVERAGE([2]DTLZ5!C4:C33)</f>
+        <v>5540</v>
+      </c>
+      <c r="G24" s="13">
+        <f>STDEV([2]DTLZ5!C4:C33)</f>
+        <v>8324.0242257182817</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="16"/>
+      <c r="C25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="5">
+        <f>AVERAGE(DTLZ5!D4:D33)</f>
+        <v>5.2434513633378645E-4</v>
+      </c>
+      <c r="E25" s="5">
+        <f>STDEV(DTLZ5!D4:D33)</f>
+        <v>9.211719935784125E-4</v>
+      </c>
+      <c r="F25" s="5">
+        <f>AVERAGE([2]DTLZ5!D4:D33)</f>
+        <v>1.1668050407066294E-3</v>
+      </c>
+      <c r="G25" s="5">
+        <f>STDEV([2]DTLZ5!D4:D33)</f>
+        <v>1.1927708306011145E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="16"/>
+      <c r="C26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5">
+        <f>AVERAGE(DTLZ5!F4:F33)</f>
+        <v>-7.1479449547621869E-4</v>
+      </c>
+      <c r="E26" s="5">
+        <f>STDEV(DTLZ5!F4:F33)</f>
+        <v>2.6688375280564292E-3</v>
+      </c>
+      <c r="F26" s="5">
+        <f>AVERAGE([2]DTLZ5!F4:F33)</f>
+        <v>-1.1999212544896028E-3</v>
+      </c>
+      <c r="G26" s="5">
+        <f>STDEV([2]DTLZ5!F4:F33)</f>
+        <v>2.2290736833031916E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="17"/>
+      <c r="C27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="11">
+        <f>AVERAGE(DTLZ5!E4:E33)</f>
+        <v>0.9646264757904931</v>
+      </c>
+      <c r="E27" s="11">
+        <f>STDEV(DTLZ5!E4:E33)</f>
+        <v>9.4941532797655284E-3</v>
+      </c>
+      <c r="F27" s="11">
+        <f>AVERAGE([2]DTLZ5!E4:E33)</f>
+        <v>0.96092424873096804</v>
+      </c>
+      <c r="G27" s="11">
+        <f>STDEV([2]DTLZ5!E4:E33)</f>
+        <v>1.2521868470254747E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B16:B19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/SC reuslts/some results NSGAII.xlsx
+++ b/SC reuslts/some results NSGAII.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahbub\Documents\GitHub\EnergyPLANDomainKnowledgeEAStep1\SC reuslts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11385" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11385"/>
   </bookViews>
   <sheets>
     <sheet name="ZDT1" sheetId="1" r:id="rId1"/>
@@ -20,7 +25,7 @@
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
   </externalReferences>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -110,8 +115,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,7 +242,17 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -270,6 +285,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -278,10 +294,12 @@
         <a:effectLst/>
       </c:spPr>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1805,14 +1823,23 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="67547136"/>
-        <c:axId val="67549056"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="296246264"/>
+        <c:axId val="296246656"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="67547136"/>
+        <c:axId val="296246264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
@@ -1854,6 +1881,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1863,6 +1891,7 @@
           </c:spPr>
         </c:title>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1894,18 +1923,19 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67549056"/>
+        <c:crossAx val="296246656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="67549056"/>
+        <c:axId val="296246656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -1947,6 +1977,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1957,6 +1988,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1988,10 +2020,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67547136"/>
+        <c:crossAx val="296246264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2005,6 +2037,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2028,7 +2061,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2341,6 +2374,87 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6819900" y="3190875"/>
+          <a:ext cx="6486525" cy="1219200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="it-IT" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>This files report the HVd,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="it-IT" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> epsd, HVper, evaluation saves parameters for each problem (tabs) when comparing with 500 generations for NSGAII. The summary tab report the summarized view of all the parameters. Please note that this file is linked to "some results SPEA2.xlsx" file (in summary tab) to provided report for SPEA2. </a:t>
+          </a:r>
+          <a:endParaRPr lang="it-IT" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2731,7 +2845,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -5242,7 +5356,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="ZDT1"/>
@@ -6942,7 +7056,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="4"/>
       <sheetData sheetId="5">
         <row r="4">
           <cell r="C4">
@@ -8047,16 +8161,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
@@ -8066,7 +8180,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -8080,7 +8194,7 @@
         <v>0.66616012487499998</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -8100,7 +8214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>0</v>
       </c>
@@ -8120,7 +8234,7 @@
         <v>-8.1951611083141897E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -8140,7 +8254,7 @@
         <v>-3.6281739877806699E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -8160,7 +8274,7 @@
         <v>4.5989107833585502E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -8180,7 +8294,7 @@
         <v>-4.6405229793171797E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -8200,7 +8314,7 @@
         <v>-1.0926191401774399E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -8220,7 +8334,7 @@
         <v>-3.8592048051273001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -8240,7 +8354,7 @@
         <v>-5.2609140308685302E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -8260,7 +8374,7 @@
         <v>-3.4882202136190901E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -8280,7 +8394,7 @@
         <v>-3.7796113035970498E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -8300,7 +8414,7 @@
         <v>-2.3133702247160599E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -8320,7 +8434,7 @@
         <v>-5.5167273454262899E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -8340,7 +8454,7 @@
         <v>-5.6387585042915103E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -8360,7 +8474,7 @@
         <v>1.5256660666840801E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -8380,7 +8494,7 @@
         <v>-6.9065711255477296E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -8424,7 +8538,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -8448,7 +8562,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -8472,7 +8586,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -8492,7 +8606,7 @@
         <v>-1.1920192462140201E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -8512,7 +8626,7 @@
         <v>-6.97531516784921E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -8532,7 +8646,7 @@
         <v>1.5421856974445701E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -8552,7 +8666,7 @@
         <v>-3.16746410373868E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -8572,7 +8686,7 @@
         <v>-4.3057009789222401E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -8592,7 +8706,7 @@
         <v>-4.0151606948934902E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -8612,7 +8726,7 @@
         <v>-1.78892856657361E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -8632,7 +8746,7 @@
         <v>-6.8941063092096098E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -8652,7 +8766,7 @@
         <v>-7.5661382731223503E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -8672,7 +8786,7 @@
         <v>-5.39067138134274E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -8692,7 +8806,7 @@
         <v>1.8114772385106001E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -8712,7 +8826,7 @@
         <v>-1.11879807624626E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -8732,7 +8846,7 @@
         <v>1.60627969693857E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -8756,9 +8870,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -8768,7 +8882,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -8782,7 +8896,7 @@
         <v>0.33283355941638099</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -8802,7 +8916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -8822,7 +8936,7 @@
         <v>-8.0974129452271405E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8842,7 +8956,7 @@
         <v>1.1177611943135001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -8862,7 +8976,7 @@
         <v>-3.2857375677534601E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -8882,7 +8996,7 @@
         <v>-2.1183220238527498E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -8902,7 +9016,7 @@
         <v>-1.8999241952578599E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -8922,7 +9036,7 @@
         <v>1.9119309980650801E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -8942,7 +9056,7 @@
         <v>-7.0782432186709196E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -8962,7 +9076,7 @@
         <v>-2.0304782157437801E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -8982,7 +9096,7 @@
         <v>-2.4605847340881601E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -9002,7 +9116,7 @@
         <v>-4.0997083396021499E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -9022,7 +9136,7 @@
         <v>-2.81743809917434E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -9042,7 +9156,7 @@
         <v>-5.5938596089526397E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -9062,7 +9176,7 @@
         <v>2.2675628621779899E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -9082,7 +9196,7 @@
         <v>-9.0659135082225796E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -9102,7 +9216,7 @@
         <v>-4.5720977475325296E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -9122,7 +9236,7 @@
         <v>-2.7016668219681499E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -9142,7 +9256,7 @@
         <v>-3.2667375157225901E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -9162,7 +9276,7 @@
         <v>5.8314486047872297E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -9182,7 +9296,7 @@
         <v>-1.7238776689698599E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -9202,7 +9316,7 @@
         <v>-9.5777867510127204E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -9222,7 +9336,7 @@
         <v>9.0615851833464301E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -9242,7 +9356,7 @@
         <v>-5.4431932951686203E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -9262,7 +9376,7 @@
         <v>-3.5403511139828702E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -9282,7 +9396,7 @@
         <v>-3.6472321048567299E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -9302,7 +9416,7 @@
         <v>2.6832081451161299E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -9322,7 +9436,7 @@
         <v>-3.5274571843107999E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -9342,7 +9456,7 @@
         <v>2.5990513066531602E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -9362,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -9382,7 +9496,7 @@
         <v>5.0382563890175496E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -9402,7 +9516,7 @@
         <v>-1.60338391865949E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -9418,7 +9532,7 @@
         <v>0.96701436612971825</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D39">
         <f>QUARTILE($D$4:$D$33,0)</f>
         <v>-2.7925113231100302E-3</v>
@@ -9432,7 +9546,7 @@
         <v>-7.0782432186709196E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D40">
         <f>QUARTILE($D$4:$D$33,1)</f>
         <v>3.9509089179294387E-4</v>
@@ -9446,7 +9560,7 @@
         <v>-3.3493909543108125E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D41">
         <f>QUARTILE($D$4:$D$33,2)</f>
         <v>2.8199461243420499E-3</v>
@@ -9460,7 +9574,7 @@
         <v>-1.7516540569586748E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D42">
         <f>QUARTILE($D$4:$D$33,3)</f>
         <v>4.2106787343501647E-3</v>
@@ -9474,7 +9588,7 @@
         <v>1.0871214720223323E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D43">
         <f>QUARTILE($D$4:$D$33,4)</f>
         <v>6.3749054886274503E-3</v>
@@ -9488,7 +9602,7 @@
         <v>5.0382563890175496E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D45">
         <f>D38-D37</f>
         <v>0</v>
@@ -9498,7 +9612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D46">
         <f>D39-D38</f>
         <v>-2.7925113231100302E-3</v>
@@ -9508,7 +9622,7 @@
         <v>7.0782432186709196E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D47">
         <f t="shared" ref="D47:D50" si="0">D40-D39</f>
         <v>3.1876022149029742E-3</v>
@@ -9518,7 +9632,7 @@
         <v>-3.7288522643601071E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D48">
         <f t="shared" si="0"/>
         <v>2.4248552325491059E-3</v>
@@ -9528,7 +9642,7 @@
         <v>-1.5977368973521377E-3</v>
       </c>
     </row>
-    <row r="49" spans="4:6">
+    <row r="49" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D49">
         <f t="shared" si="0"/>
         <v>1.3907326100081148E-3</v>
@@ -9538,7 +9652,7 @@
         <v>-1.860366204160908E-3</v>
       </c>
     </row>
-    <row r="50" spans="4:6">
+    <row r="50" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D50">
         <f t="shared" si="0"/>
         <v>2.1642267542772856E-3</v>
@@ -9555,9 +9669,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -9567,7 +9681,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -9581,7 +9695,7 @@
         <v>0.51719187154758695</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -9601,7 +9715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -9621,7 +9735,7 @@
         <v>-1.2119754075568499E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -9641,7 +9755,7 @@
         <v>-5.9026780993743999E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -9661,7 +9775,7 @@
         <v>1.31836055900639E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -9681,7 +9795,7 @@
         <v>-1.67674038697403E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -9701,7 +9815,7 @@
         <v>-1.0142672573018E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -9721,7 +9835,7 @@
         <v>-1.2517411531936799E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -9741,7 +9855,7 @@
         <v>1.9154975424234199E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -9761,7 +9875,7 @@
         <v>-6.99970418727946E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -9781,7 +9895,7 @@
         <v>-3.2579873770000002E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -9801,7 +9915,7 @@
         <v>-2.6419898658634998E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -9821,7 +9935,7 @@
         <v>-1.3954769173487499E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -9841,7 +9955,7 @@
         <v>-4.8550550644500803E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -9861,7 +9975,7 @@
         <v>-5.0990232070927399E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -9881,7 +9995,7 @@
         <v>-1.7819612863766499E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -9901,7 +10015,7 @@
         <v>-1.1371158191845501E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -9921,7 +10035,7 @@
         <v>3.9224771035693801E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -9941,7 +10055,7 @@
         <v>-1.3571533176202999E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -9961,7 +10075,7 @@
         <v>-2.6017640606640298E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -9981,7 +10095,7 @@
         <v>-5.7224645484128204E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -10001,7 +10115,7 @@
         <v>-8.8889988539172793E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -10021,7 +10135,7 @@
         <v>-5.8806215826587198E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -10041,7 +10155,7 @@
         <v>-2.59241435319469E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -10061,7 +10175,7 @@
         <v>-6.6292179250593501E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -10081,7 +10195,7 @@
         <v>-1.0078287593559099E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -10101,7 +10215,7 @@
         <v>-6.3987936206359999E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -10121,7 +10235,7 @@
         <v>-8.1884611163008502E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -10141,7 +10255,7 @@
         <v>-8.6311564224213905E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -10161,7 +10275,7 @@
         <v>-8.2549595578293705E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -10181,7 +10295,7 @@
         <v>-1.08959930176485E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -10201,7 +10315,7 @@
         <v>-7.0021476630840996E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -10217,7 +10331,7 @@
         <v>0.98451978129199669</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D39">
         <f>QUARTILE($D$4:$D$33,0)</f>
         <v>-5.6410577857612899E-4</v>
@@ -10227,7 +10341,7 @@
         <v>-1.3954769173487499E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D40">
         <f>QUARTILE($D$4:$D$33,1)</f>
         <v>2.1502800157512875E-3</v>
@@ -10237,7 +10351,7 @@
         <v>-7.8912718840455018E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D41">
         <f>QUARTILE($D$4:$D$33,2)</f>
         <v>4.4350223274996449E-3</v>
@@ -10247,7 +10361,7 @@
         <v>-4.9770391357714105E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42">
         <f>QUARTILE($D$4:$D$33,3)</f>
         <v>6.0704804641376602E-3</v>
@@ -10257,7 +10371,7 @@
         <v>-1.1201933282128499E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43">
         <f>QUARTILE($D$4:$D$33,4)</f>
         <v>1.06046338090119E-2</v>
@@ -10267,7 +10381,7 @@
         <v>1.9154975424234199E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45">
         <f>D38-D37</f>
         <v>0</v>
@@ -10277,7 +10391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D46">
         <f>D39-D38</f>
         <v>-5.6410577857612899E-4</v>
@@ -10287,7 +10401,7 @@
         <v>-1.3954769173487499E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D47">
         <f t="shared" ref="D47:F50" si="0">D40-D39</f>
         <v>2.7143857943274165E-3</v>
@@ -10297,7 +10411,7 @@
         <v>6.0634972894419974E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D48">
         <f t="shared" si="0"/>
         <v>2.2847423117483574E-3</v>
@@ -10307,7 +10421,7 @@
         <v>2.9142327482740912E-3</v>
       </c>
     </row>
-    <row r="49" spans="4:6">
+    <row r="49" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D49">
         <f t="shared" si="0"/>
         <v>1.6354581366380154E-3</v>
@@ -10317,7 +10431,7 @@
         <v>3.8568458075585606E-3</v>
       </c>
     </row>
-    <row r="50" spans="4:6">
+    <row r="50" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D50">
         <f t="shared" si="0"/>
         <v>4.5341533448742394E-3</v>
@@ -10334,9 +10448,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -10346,7 +10460,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -10360,7 +10474,7 @@
         <v>0.66617361728492197</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -10380,7 +10494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -10400,7 +10514,7 @@
         <v>4.0554145517913099E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -10420,7 +10534,7 @@
         <v>0.279595935073226</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -10440,7 +10554,7 @@
         <v>-1.8706740924329099E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -10460,7 +10574,7 @@
         <v>-3.2570612161153501E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -10480,7 +10594,7 @@
         <v>-0.25458930937267898</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -10500,7 +10614,7 @@
         <v>-0.21675477052320299</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -10520,7 +10634,7 @@
         <v>2.91664938337582E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -10540,7 +10654,7 @@
         <v>0.104297651062652</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -10560,7 +10674,7 @@
         <v>4.3715158959601796E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -10580,7 +10694,7 @@
         <v>-3.91949096680555E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -10600,7 +10714,7 @@
         <v>1.91910487543472E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -10620,7 +10734,7 @@
         <v>-6.0679295346903099E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -10640,7 +10754,7 @@
         <v>3.9748435611588204E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -10660,7 +10774,7 @@
         <v>5.7916706645013598E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -10680,7 +10794,7 @@
         <v>4.2894481460590802E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -10700,7 +10814,7 @@
         <v>7.8711482512001205E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -10720,7 +10834,7 @@
         <v>1.4486254408815299E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -10740,7 +10854,7 @@
         <v>9.8627864801995702E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -10760,7 +10874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -10780,7 +10894,7 @@
         <v>-9.7910468117792998E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -10800,7 +10914,7 @@
         <v>4.7719312585747797E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -10820,7 +10934,7 @@
         <v>2.1047689339612698E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -10840,7 +10954,7 @@
         <v>-5.5136005584197002E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -10860,7 +10974,7 @@
         <v>-7.6083237656365799E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -10880,7 +10994,7 @@
         <v>5.2323261747570697E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -10900,7 +11014,7 @@
         <v>0.131960652140344</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -10920,7 +11034,7 @@
         <v>5.1836604315231599E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -10940,7 +11054,7 @@
         <v>-1.80039045323332E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -10960,7 +11074,7 @@
         <v>6.6104754297627803E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -10980,7 +11094,7 @@
         <v>0.27240253349211102</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -11003,9 +11117,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -11015,7 +11129,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -11029,7 +11143,7 @@
         <v>0.40590724234006298</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -11049,7 +11163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -11069,7 +11183,7 @@
         <v>3.8198108154760902E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -11089,7 +11203,7 @@
         <v>-1.2142214752381799</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -11109,7 +11223,7 @@
         <v>-7.0074214958807002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -11129,7 +11243,7 @@
         <v>9.3640710508028097E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -11149,7 +11263,7 @@
         <v>-1.1840350230275001</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -11169,7 +11283,7 @@
         <v>-0.34271872271019399</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -11189,7 +11303,7 @@
         <v>1.54688456743761E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -11209,7 +11323,7 @@
         <v>-2.01434853155701E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -11229,7 +11343,7 @@
         <v>1.4505734973628399E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -11249,7 +11363,7 @@
         <v>8.9788680184770594E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -11269,7 +11383,7 @@
         <v>1.5916220751723699E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -11289,7 +11403,7 @@
         <v>-0.31100727658218902</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -11309,7 +11423,7 @@
         <v>-5.0674695337909699E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -11329,7 +11443,7 @@
         <v>-8.5323927216879494E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -11349,7 +11463,7 @@
         <v>1.5645896908951299E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -11369,7 +11483,7 @@
         <v>-2.3754180001397399E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -11389,7 +11503,7 @@
         <v>-1.06692643429668</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -11409,7 +11523,7 @@
         <v>1.6243311531219599E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -11429,7 +11543,7 @@
         <v>-0.46301180079864301</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -11449,7 +11563,7 @@
         <v>-1.69854676244289</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -11469,7 +11583,7 @@
         <v>-0.94912546798061004</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -11489,7 +11603,7 @@
         <v>-1.80430025814446</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -11509,7 +11623,7 @@
         <v>1.33636024190034E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -11529,7 +11643,7 @@
         <v>-0.25131193831996201</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -11549,7 +11663,7 @@
         <v>-0.48756962261563502</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -11569,7 +11683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -11589,7 +11703,7 @@
         <v>-2.6095160997089502E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -11609,7 +11723,7 @@
         <v>-0.74697105233851402</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -11629,7 +11743,7 @@
         <v>1.8625747914139301E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -11649,7 +11763,7 @@
         <v>-0.38463177904765999</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -11665,7 +11779,7 @@
         <v>0.57649171111802644</v>
       </c>
     </row>
-    <row r="55" spans="6:6">
+    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F55" s="1"/>
     </row>
   </sheetData>
@@ -11680,9 +11794,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -11692,7 +11806,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -11706,7 +11820,7 @@
         <v>0.46783583650461702</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -11726,7 +11840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -11746,7 +11860,7 @@
         <v>-3.6535029671500102E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -11766,7 +11880,7 @@
         <v>1.4675506133468E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -11786,7 +11900,7 @@
         <v>-2.3010561786476701E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -11806,7 +11920,7 @@
         <v>-2.9082730606477199E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -11826,7 +11940,7 @@
         <v>3.3547020427374799E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -11846,7 +11960,7 @@
         <v>-2.7226830001258098E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -11866,7 +11980,7 @@
         <v>1.47153077308439E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -11886,7 +12000,7 @@
         <v>2.6752615165469101E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -11906,7 +12020,7 @@
         <v>4.3015006239444598E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -11926,7 +12040,7 @@
         <v>-1.2398493184265801E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -11946,7 +12060,7 @@
         <v>-1.1238123454104E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -11966,7 +12080,7 @@
         <v>-6.4259516686617701E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -11986,7 +12100,7 @@
         <v>-1.5040684506399201E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -12006,7 +12120,7 @@
         <v>1.1710418563115599E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -12026,7 +12140,7 @@
         <v>-1.8614187586653699E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -12046,7 +12160,7 @@
         <v>-2.11779337502087E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -12066,7 +12180,7 @@
         <v>2.9152638894912502E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -12086,7 +12200,7 @@
         <v>9.1143764287142798E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -12106,7 +12220,7 @@
         <v>2.9163089003310799E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -12126,7 +12240,7 @@
         <v>-7.3466645591996305E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -12146,7 +12260,7 @@
         <v>-1.4474323063490099E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -12166,7 +12280,7 @@
         <v>-1.4666085283480399E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -12186,7 +12300,7 @@
         <v>5.4873279348653901E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -12206,7 +12320,7 @@
         <v>3.3292849450299498E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -12226,7 +12340,7 @@
         <v>1.8729859539121201E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -12246,7 +12360,7 @@
         <v>2.3295079612731802E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -12266,7 +12380,7 @@
         <v>-8.20997221326214E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -12286,7 +12400,7 @@
         <v>7.7431777921155298E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -12306,7 +12420,7 @@
         <v>3.8305146468709902E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -12326,7 +12440,7 @@
         <v>-1.21740165450427E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -12349,9 +12463,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -12361,7 +12475,7 @@
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -12375,7 +12489,7 @@
         <v>9.5583254269994297E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -12395,7 +12509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
@@ -12415,7 +12529,7 @@
         <v>2.27901221423021E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -12435,7 +12549,7 @@
         <v>2.31108570802218E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -12455,7 +12569,7 @@
         <v>2.55072751944751E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -12475,7 +12589,7 @@
         <v>1.33229755167912E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -12495,7 +12609,7 @@
         <v>-2.8956791023078102E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -12515,7 +12629,7 @@
         <v>1.55060996987099E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -12535,7 +12649,7 @@
         <v>1.3370711879616599E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -12555,7 +12669,7 @@
         <v>-2.64351000704543E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -12575,7 +12689,7 @@
         <v>-1.7008091382262299E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -12595,7 +12709,7 @@
         <v>-4.7348999076028903E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
@@ -12615,7 +12729,7 @@
         <v>-1.9583094439135001E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
@@ -12635,7 +12749,7 @@
         <v>-1.01979899980586E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12</v>
       </c>
@@ -12655,7 +12769,7 @@
         <v>-1.6976618436987301E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>13</v>
       </c>
@@ -12675,7 +12789,7 @@
         <v>1.3509037897166899E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14</v>
       </c>
@@ -12695,7 +12809,7 @@
         <v>-4.0251692337766598E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>15</v>
       </c>
@@ -12715,7 +12829,7 @@
         <v>-3.9144852080597002E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>16</v>
       </c>
@@ -12735,7 +12849,7 @@
         <v>-1.2018872661650401E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
@@ -12755,7 +12869,7 @@
         <v>6.9685420040077595E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
@@ -12775,7 +12889,7 @@
         <v>8.8558447095388095E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>19</v>
       </c>
@@ -12795,7 +12909,7 @@
         <v>3.3914477067993301E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -12815,7 +12929,7 @@
         <v>-3.6699534450201901E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -12835,7 +12949,7 @@
         <v>1.6901728547010701E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -12855,7 +12969,7 @@
         <v>3.5566008574485701E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>23</v>
       </c>
@@ -12875,7 +12989,7 @@
         <v>2.34240809806618E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>24</v>
       </c>
@@ -12895,7 +13009,7 @@
         <v>-3.8331853111473698E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25</v>
       </c>
@@ -12915,7 +13029,7 @@
         <v>-4.2334451023048301E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26</v>
       </c>
@@ -12935,7 +13049,7 @@
         <v>1.35265354365587E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>27</v>
       </c>
@@ -12955,7 +13069,7 @@
         <v>-2.94054514192437E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
@@ -12975,7 +13089,7 @@
         <v>-6.8809596209191597E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>29</v>
       </c>
@@ -12995,7 +13109,7 @@
         <v>-5.1583751087591601E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -13017,11 +13131,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:9">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
@@ -13035,7 +13149,7 @@
       </c>
       <c r="G2" s="14"/>
     </row>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="6" t="s">
@@ -13051,7 +13165,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
         <v>11</v>
       </c>
@@ -13075,7 +13189,7 @@
         <v>7159.1722375171821</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="16"/>
       <c r="C5" s="9" t="s">
         <v>13</v>
@@ -13101,7 +13215,7 @@
         <v>5.2434513633378645E-4</v>
       </c>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="16"/>
       <c r="C6" s="9" t="s">
         <v>14</v>
@@ -13127,7 +13241,7 @@
         <v>8.797703848114102E-3</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="17"/>
       <c r="C7" s="10" t="s">
         <v>16</v>
@@ -13149,7 +13263,7 @@
         <v>3.6099371088204111E-3</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
         <v>18</v>
       </c>
@@ -13173,7 +13287,7 @@
         <v>11295.447664038575</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
       <c r="C9" s="9" t="s">
         <v>13</v>
@@ -13195,7 +13309,7 @@
         <v>1.4868639033140696E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="16"/>
       <c r="C10" s="9" t="s">
         <v>14</v>
@@ -13217,7 +13331,7 @@
         <v>0.12172660266913846</v>
       </c>
     </row>
-    <row r="11" spans="2:9">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="17"/>
       <c r="C11" s="10" t="s">
         <v>16</v>
@@ -13239,7 +13353,7 @@
         <v>5.7688357787110244E-3</v>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
         <v>20</v>
       </c>
@@ -13263,7 +13377,7 @@
         <v>9862.3957827047598</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="16"/>
       <c r="C13" s="9" t="s">
         <v>13</v>
@@ -13285,7 +13399,7 @@
         <v>1.4358361485530238E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="16"/>
       <c r="C14" s="9" t="s">
         <v>14</v>
@@ -13307,7 +13421,7 @@
         <v>2.4086556702087061E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="17"/>
       <c r="C15" s="10" t="s">
         <v>16</v>
@@ -13329,7 +13443,7 @@
         <v>2.7756297086266094E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>19</v>
       </c>
@@ -13353,7 +13467,7 @@
         <v>11662.834674455355</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="16"/>
       <c r="C17" s="9" t="s">
         <v>13</v>
@@ -13375,7 +13489,7 @@
         <v>0.14256837030049149</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="16"/>
       <c r="C18" s="9" t="s">
         <v>14</v>
@@ -13397,7 +13511,7 @@
         <v>0.30035859770009959</v>
       </c>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="10" t="s">
         <v>16</v>
@@ -13419,7 +13533,7 @@
         <v>0.19898209936606981</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>21</v>
       </c>
@@ -13443,7 +13557,7 @@
         <v>6152.0915049320811</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="16"/>
       <c r="C21" s="9" t="s">
         <v>13</v>
@@ -13465,7 +13579,7 @@
         <v>4.8120945537095663E-3</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="16"/>
       <c r="C22" s="9" t="s">
         <v>14</v>
@@ -13487,7 +13601,7 @@
         <v>1.1788804032500315E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="17"/>
       <c r="C23" s="10" t="s">
         <v>16</v>
@@ -13509,7 +13623,7 @@
         <v>8.9307924910633947E-3</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
@@ -13533,7 +13647,7 @@
         <v>8324.0242257182817</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="16"/>
       <c r="C25" s="9" t="s">
         <v>13</v>
@@ -13555,7 +13669,7 @@
         <v>1.1927708306011145E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="16"/>
       <c r="C26" s="9" t="s">
         <v>14</v>
@@ -13577,7 +13691,7 @@
         <v>2.2290736833031916E-3</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="17"/>
       <c r="C27" s="10" t="s">
         <v>16</v>
